--- a/tame_output/ON/bt/strategyON_20240919.xlsx
+++ b/tame_output/ON/bt/strategyON_20240919.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-70.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.4%</t>
+          <t>-581.6%</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.5%</t>
+          <t>-322.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.5%</t>
+          <t>131.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.331941497271198</v>
+        <v>-4.422888068417722</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.746895511958366</v>
+        <v>1.710516883499756</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9750965143537189</v>
+        <v>0.8841499432071951</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.065086443792825</v>
+        <v>4.010518501104911</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.254842895729325</v>
+        <v>-4.345789466875849</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.776922663011545</v>
+        <v>1.740544034552935</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9750965143537189</v>
+        <v>0.8841499432071951</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.064274154229254</v>
+        <v>4.00970621154134</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.265228090619215</v>
+        <v>-4.356174661765738</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.782637364180661</v>
+        <v>1.746258735722052</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9647113194638296</v>
+        <v>0.8737647483173058</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.067911816420393</v>
+        <v>4.013343873732479</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.28381624934144</v>
+        <v>-4.374762820487963</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.846039106468196</v>
+        <v>1.809660478009587</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9461231607416043</v>
+        <v>0.8551765895950805</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.127595926963483</v>
+        <v>4.073027984275569</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.284114796037476</v>
+        <v>-4.375061367183999</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.842788698608081</v>
+        <v>1.806410070149471</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9458246140455684</v>
+        <v>0.8548780428990446</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.12428580976416</v>
+        <v>4.069717867076246</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.183291662347048</v>
+        <v>-4.274238233493572</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.887648847023643</v>
+        <v>1.851270218565034</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9582888295299222</v>
+        <v>0.8673422583833984</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.136295233994164</v>
+        <v>4.081727291306249</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.992510301594641</v>
+        <v>-4.083456872741165</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.964090644803149</v>
+        <v>1.92771201634454</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.149070190282329</v>
+        <v>1.058123619135806</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.250893303924151</v>
+        <v>4.196325361236237</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.885546943745219</v>
+        <v>-3.976493514891743</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.986712833680515</v>
+        <v>1.950334205221905</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.207534798242131</v>
+        <v>1.116588227095607</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.265808914437629</v>
+        <v>4.211240971749715</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.830216355843457</v>
+        <v>-3.921162926989981</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.043812005453278</v>
+        <v>2.007433376994668</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.262865386143893</v>
+        <v>1.171918814997369</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.333974203790745</v>
+        <v>4.279406261102831</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.818162228930494</v>
+        <v>-3.909108800077018</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.042320224119901</v>
+        <v>2.005941595661291</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.274919513056856</v>
+        <v>1.183972941910332</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.33489324783996</v>
+        <v>4.280325305152046</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.859317348498715</v>
+        <v>-3.950263919645239</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.027738806476748</v>
+        <v>1.991360178018138</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.233764393488635</v>
+        <v>1.142817822342111</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.312080806283164</v>
+        <v>4.257512863595249</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.791268785807185</v>
+        <v>-3.882215356953709</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.067809257431243</v>
+        <v>2.031430628972633</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.301812956180165</v>
+        <v>1.210866385033641</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.365760969775963</v>
+        <v>4.311193027088049</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.022869178976686</v>
+        <v>-4.11381575012321</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.995371770337036</v>
+        <v>1.958993141878427</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.301812956180165</v>
+        <v>1.210866385033641</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.385963639949558</v>
+        <v>4.331395697261644</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.072920724505906</v>
+        <v>-4.16386729565243</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.958957388192231</v>
+        <v>1.922578759733621</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.301812956180165</v>
+        <v>1.210866385033641</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.36956987601644</v>
+        <v>4.315001933328526</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.24802755708235</v>
+        <v>-4.338974128228875</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.849166568755119</v>
+        <v>1.812787940296509</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.301812956180165</v>
+        <v>1.210866385033641</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.329821789609906</v>
+        <v>4.275253846921992</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.051927403651828</v>
+        <v>-4.142873974798352</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.934629249124268</v>
+        <v>1.898250620665659</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.497913109610688</v>
+        <v>1.406966538464164</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.45450450066516</v>
+        <v>4.399936557977246</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.898902011538544</v>
+        <v>-3.989848582685068</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.095010405542487</v>
+        <v>2.058631777083876</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.650938501723972</v>
+        <v>1.559991930577448</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.645490735506035</v>
+        <v>4.590922792818121</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.927209325411813</v>
+        <v>-4.018155896558338</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.271153704901471</v>
+        <v>2.234775076442861</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.650938501723972</v>
+        <v>1.559991930577448</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.832956960414328</v>
+        <v>4.778389017726414</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.093802550525336</v>
+        <v>-4.18474912167186</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.173919366210145</v>
+        <v>2.137540737751535</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.484345276610449</v>
+        <v>1.393398705463926</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.702403976700297</v>
+        <v>4.647836034012383</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.07076675716377</v>
+        <v>-4.161713328310294</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.186810086216489</v>
+        <v>2.150431457757879</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.484345276610449</v>
+        <v>1.393398705463926</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.706080379362015</v>
+        <v>4.651512436674101</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.041520776708073</v>
+        <v>-4.132467347854598</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.196126533522263</v>
+        <v>2.159747905063653</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.484345276610449</v>
+        <v>1.393398705463926</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.70369843448551</v>
+        <v>4.649130491797596</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.148446324585924</v>
+        <v>-4.239392895732449</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.150649553528758</v>
+        <v>2.114270925070148</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.377419728732598</v>
+        <v>1.286473157586074</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.636836344916434</v>
+        <v>4.58226840222852</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.293464883093173</v>
+        <v>-4.384411454239697</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.094070932269092</v>
+        <v>2.057692303810482</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.232401170225349</v>
+        <v>1.141454599078826</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.55125401195532</v>
+        <v>4.496686069267406</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.41180664887789</v>
+        <v>-4.502753220024415</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.146665465212958</v>
+        <v>2.110286836754348</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.24308720878824</v>
+        <v>1.152140637641716</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.657596874350807</v>
+        <v>4.603028931662893</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.463217071198598</v>
+        <v>-4.554163642345123</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.123886993410614</v>
+        <v>2.087508364952004</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.24308720878824</v>
+        <v>1.152140637641716</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.655382571476745</v>
+        <v>4.600814628788831</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.54263652240635</v>
+        <v>-4.633583093552875</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.092022341001803</v>
+        <v>2.055643712543193</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.24308720878824</v>
+        <v>1.152140637641716</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.655285699551035</v>
+        <v>4.600717756863121</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.638099520323568</v>
+        <v>-4.729046091470092</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.053831035392959</v>
+        <v>2.017452406934349</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.24308720878824</v>
+        <v>1.152140637641716</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.655279593109078</v>
+        <v>4.600711650421164</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.573723609472853</v>
+        <v>-4.664670180619377</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.077677796295855</v>
+        <v>2.041299167837245</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.307463119638955</v>
+        <v>1.216516548492431</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.692001536182118</v>
+        <v>4.637433593494203</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.629092771605047</v>
+        <v>-4.720039342751571</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.061263949190704</v>
+        <v>2.024885320732094</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.307463119638955</v>
+        <v>1.216516548492431</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.697735353929844</v>
+        <v>4.643167411241929</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.674530551435874</v>
+        <v>-4.765477122582398</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.042627200601306</v>
+        <v>2.006248572142696</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.264618128960795</v>
+        <v>1.173671557814272</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.67156672286588</v>
+        <v>4.616998780177966</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.586323717288296</v>
+        <v>-4.67727028843482</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.097784327110656</v>
+        <v>2.061405698652046</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.264618128960795</v>
+        <v>1.173671557814272</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.691441115716199</v>
+        <v>4.636873173028285</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.480288722082986</v>
+        <v>-4.571235293229511</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.123899025717507</v>
+        <v>2.087520397258897</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.264618128960795</v>
+        <v>1.173671557814272</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.675141816240927</v>
+        <v>4.620573873553013</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.297077058949891</v>
+        <v>-4.388023630096415</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.199614640434791</v>
+        <v>2.163236011976181</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.264618128960795</v>
+        <v>1.173671557814272</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.677572765704973</v>
+        <v>4.623004823017059</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.22535561193604</v>
+        <v>-4.316302183082565</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.194094405088221</v>
+        <v>2.157715776629611</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.336339575974646</v>
+        <v>1.245393004828122</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.686396819761173</v>
+        <v>4.631828877073259</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.202982586328334</v>
+        <v>-4.293929157474858</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.149959361252475</v>
+        <v>2.113580732793865</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.347595327087547</v>
+        <v>1.256648755941024</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.640066016350086</v>
+        <v>4.585498073662172</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.235998882239079</v>
+        <v>-4.326945453385603</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.321951047773533</v>
+        <v>2.285572419314922</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.278157950420796</v>
+        <v>1.187211379274272</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.78360179523539</v>
+        <v>4.729033852547476</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.22447124658947</v>
+        <v>-4.315417817735995</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.318483327861625</v>
+        <v>2.282104699403015</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.337158608622158</v>
+        <v>1.246212037475635</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.810923415984456</v>
+        <v>4.756355473296543</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.321812747931839</v>
+        <v>-4.412759319078363</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.283214839846466</v>
+        <v>2.246836211387857</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.29273842645667</v>
+        <v>1.201791855310146</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.787939419206952</v>
+        <v>4.733371476519038</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.407668777271805</v>
+        <v>-4.49861534841833</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.250123510303318</v>
+        <v>2.213744881844708</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.250362357230535</v>
+        <v>1.159415786084011</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.763764859864109</v>
+        <v>4.709196917176195</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.416505574687925</v>
+        <v>-4.507452145834449</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.229007993157372</v>
+        <v>2.192629364698762</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.242920184589184</v>
+        <v>1.151973613442661</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.7417187580998</v>
+        <v>4.687150815411886</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.507888137253383</v>
+        <v>-4.598834708399908</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.202619479176238</v>
+        <v>2.166240850717628</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.206355299869839</v>
+        <v>1.115408728723316</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.729944338313243</v>
+        <v>4.675376395625329</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.496181419266377</v>
+        <v>-4.587127990412902</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.309430424195307</v>
+        <v>2.273051795736698</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.218062017856846</v>
+        <v>1.127115446710322</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.839096626929714</v>
+        <v>4.7845286842418</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.396517915182715</v>
+        <v>-4.487464486329239</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.352328164560177</v>
+        <v>2.315949536101567</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.281249101060532</v>
+        <v>1.190302529914009</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.880041215583331</v>
+        <v>4.825473272895417</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.406834013349067</v>
+        <v>-4.497780584495591</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.561106558571694</v>
+        <v>2.524727930113085</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.281249101060532</v>
+        <v>1.190302529914009</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.092946048861389</v>
+        <v>5.038378106173475</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.406740045331694</v>
+        <v>-4.497686616478219</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.560322812690734</v>
+        <v>2.523944184232124</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.28161896240785</v>
+        <v>1.190672391261327</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.09234663258187</v>
+        <v>5.037778689893956</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.413958869531538</v>
+        <v>-4.504905440678063</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.551667268955149</v>
+        <v>2.515288640496539</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.28161896240785</v>
+        <v>1.190672391261327</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.086578618526223</v>
+        <v>5.032010675838309</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.4130104464135</v>
+        <v>-4.503957017560024</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.552046638202365</v>
+        <v>2.515668009743755</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.28161896240785</v>
+        <v>1.190672391261327</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.086578618526223</v>
+        <v>5.032010675838309</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.570078904669124</v>
+        <v>-4.661025475815649</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.501946862881207</v>
+        <v>2.465568234422597</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.28161896240785</v>
+        <v>1.190672391261327</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.099306226507315</v>
+        <v>5.044738283819401</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.564086657880313</v>
+        <v>-4.655033229026837</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.50628976002112</v>
+        <v>2.46991113156251</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.28161896240785</v>
+        <v>1.190672391261327</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.101252224931703</v>
+        <v>5.046684282243789</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.475528696749545</v>
+        <v>-4.566475267896069</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.535367080491195</v>
+        <v>2.498988452032585</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.28161896240785</v>
+        <v>1.190672391261327</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.094906360949472</v>
+        <v>5.040338418261558</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.457769619246471</v>
+        <v>-4.548716190392995</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.54177938893142</v>
+        <v>2.505400760472811</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.28161896240785</v>
+        <v>1.190672391261327</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.094215038388468</v>
+        <v>5.039647095700554</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.358139468197403</v>
+        <v>-4.449086039343928</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.594413635259635</v>
+        <v>2.558035006801025</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.381249113456918</v>
+        <v>1.290302542310394</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.166775314926495</v>
+        <v>5.112207372238581</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.407538976886414</v>
+        <v>-4.498485548032939</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.763808097282757</v>
+        <v>2.727429468824146</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.391507946888663</v>
+        <v>1.300561375742139</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.362084880484268</v>
+        <v>5.307516937796354</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.200854503244038</v>
+        <v>-4.291801074390563</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.833670559842569</v>
+        <v>2.797291931383959</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.598192420531038</v>
+        <v>1.507245849384515</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.473284237772556</v>
+        <v>5.418716295084641</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.235011398241564</v>
+        <v>-4.325957969388089</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.822009315497664</v>
+        <v>2.785630687039053</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.514608650990226</v>
+        <v>1.423662079843703</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.425135489702173</v>
+        <v>5.370567547014259</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.142421919180108</v>
+        <v>-4.233368490326632</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.212542221111914</v>
+        <v>3.176163592653304</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.514608650990226</v>
+        <v>1.423662079843703</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.778632603691841</v>
+        <v>5.724064661003927</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.872153244391432</v>
+        <v>3.803900228361023</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.198748090984244</v>
+        <v>-4.199951108651147</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.194574863957362</v>
+        <v>3.194093656890601</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.500528766467636</v>
+        <v>1.500775311798835</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.77474778454539</v>
+        <v>5.774895711744109</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240919.xlsx
+++ b/tame_output/ON/bt/strategyON_20240919.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.6%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.6%</t>
+          <t>-590.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-60.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.5%</t>
+          <t>-322.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-83.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.6%</t>
+          <t>129.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120.1%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>131.5%</t>
+          <t>126.0%</t>
         </is>
       </c>
     </row>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
@@ -49644,16 +49644,16 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.199951108651147</v>
+        <v>-4.293257118150183</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.194093656890601</v>
+        <v>3.156771253090987</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.500775311798835</v>
+        <v>1.409540165156238</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.774895711744109</v>
+        <v>5.720154623758551</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240919.xlsx
+++ b/tame_output/ON/bt/strategyON_20240919.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>114.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>175.8%</t>
+          <t>180.6%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.5%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2091"/>
+  <dimension ref="A1:G2092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.803900228361023</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
@@ -49654,6 +49654,29 @@
       </c>
       <c r="G2091" t="n">
         <v>5.720154623758551</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="2" t="n">
+        <v>45554</v>
+      </c>
+      <c r="B2092" t="n">
+        <v>3.804033687708811</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>4.922466024393564</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>-4.293257118150183</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>3.156771253090987</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>1.409540165156238</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>4.915529821379931</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240919.xlsx
+++ b/tame_output/ON/bt/strategyON_20240919.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.7%</t>
+          <t>111.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.6%</t>
+          <t>172.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-590.9%</t>
+          <t>-595.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-60.5%</t>
+          <t>-62.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.9%</t>
+          <t>-322.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-83.0%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>37.8%</t>
         </is>
       </c>
     </row>
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.5658078899723</v>
+        <v>-2.606424982612299</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.182451473205566</v>
+        <v>2.166204636149566</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.263827726285738</v>
+        <v>1.223210633645739</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.967427689279677</v>
+        <v>3.943057433695677</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.642137867573206</v>
+        <v>-2.682754960213205</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.150031295058978</v>
+        <v>2.133784458002979</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.263827726285738</v>
+        <v>1.223210633645739</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.965539502173452</v>
+        <v>3.941169246589452</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.735801812250747</v>
+        <v>-2.776418904890746</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.107385946790824</v>
+        <v>2.091139109734825</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.170163781608197</v>
+        <v>1.129546688968198</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.904161364969789</v>
+        <v>3.87979110938579</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.897370237778002</v>
+        <v>-2.937987330418002</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.041192586790075</v>
+        <v>2.024945749734075</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.043380857810317</v>
+        <v>1.002763765170318</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.826525620901214</v>
+        <v>3.802155365317215</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.005670899648122</v>
+        <v>-3.046287992288121</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.010945728907945</v>
+        <v>1.994698891851946</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.043380857810317</v>
+        <v>1.002763765170318</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.839599027767133</v>
+        <v>3.815228772183133</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.023474871368866</v>
+        <v>-3.064091964008865</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.995829337002588</v>
+        <v>1.979582499946588</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9728462349051163</v>
+        <v>0.932229142265117</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.789283450806952</v>
+        <v>3.764913195222952</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.051375658478339</v>
+        <v>-3.091992751118338</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.983193063285801</v>
+        <v>1.966946226229801</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9382493107621815</v>
+        <v>0.8976322181221822</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.767049337448193</v>
+        <v>3.742679081864194</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.173901761181233</v>
+        <v>-3.214518853821232</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.930947066181842</v>
+        <v>1.914700229125842</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8157232080592877</v>
+        <v>0.7751061154192883</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.690298119803656</v>
+        <v>3.665927864219656</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.404416257366822</v>
+        <v>-3.44503335000682</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.90544722729811</v>
+        <v>1.88920039024211</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5852087118736989</v>
+        <v>0.5445916192336996</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.618695381682806</v>
+        <v>3.594325126098806</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.753161342591265</v>
+        <v>-3.793778435231264</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.906260912210179</v>
+        <v>1.89001407515418</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4358436653148018</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.693758328333314</v>
+        <v>3.669388072749315</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.907147760367406</v>
+        <v>-3.947764853007405</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.913646614245363</v>
+        <v>1.897399777189364</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4358436653148018</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.762738597478954</v>
+        <v>3.738368341894954</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.111747195230414</v>
+        <v>-4.152364287870413</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.81785804242028</v>
+        <v>1.801611205364281</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4358436653148018</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.748789799599075</v>
+        <v>3.724419544015075</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.364222349238139</v>
+        <v>-4.404839441878138</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.728738469872605</v>
+        <v>1.712491632816605</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4358436653148018</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.760660288654489</v>
+        <v>3.736290033070489</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.657118105717551</v>
+        <v>-4.69773519835755</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.612790701799784</v>
+        <v>1.596543864743784</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4358436653148018</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.761870823173433</v>
+        <v>3.737500567589433</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.843782233852359</v>
+        <v>-4.884399326492358</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.542246792773182</v>
+        <v>1.525999955717182</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4497217871302412</v>
+        <v>0.4091046944902419</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.749949182906018</v>
+        <v>3.725578927322019</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.989802920766321</v>
+        <v>-5.03042001340632</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.478916370743786</v>
+        <v>1.462669533687787</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4406386953363843</v>
+        <v>0.4000216026963849</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.739577180565893</v>
+        <v>3.715206924981894</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.081516929875907</v>
+        <v>-5.122134022515905</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.604434823798996</v>
+        <v>1.588187986742997</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4406386953363843</v>
+        <v>0.4000216026963849</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.901781237264938</v>
+        <v>3.877410981680938</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.113168588935876</v>
+        <v>-5.153785681575874</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.586620798138823</v>
+        <v>1.570373961082824</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4354702380919441</v>
+        <v>0.3948531454519447</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.893526800882088</v>
+        <v>3.869156545298088</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.182234643508813</v>
+        <v>-5.222851736148811</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.569223793878139</v>
+        <v>1.55297695682214</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.373099360598334</v>
+        <v>0.3324822679583347</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.866333691954413</v>
+        <v>3.841963436370413</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.28421076575722</v>
+        <v>-5.324827858397218</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.537358983434678</v>
+        <v>1.521112146378679</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2711232383499265</v>
+        <v>0.2305061457099271</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.814073657061271</v>
+        <v>3.789703401477271</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.174204482279999</v>
+        <v>-5.214821574919997</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.573514384069743</v>
+        <v>1.557267547013743</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2943278102672017</v>
+        <v>0.2537107176272023</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.820149287455811</v>
+        <v>3.795779031871811</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.031144906539073</v>
+        <v>-5.071761999179071</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.634988225088087</v>
+        <v>1.618741388032088</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.302341236857181</v>
+        <v>0.2617241442171816</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.829207354131773</v>
+        <v>3.804837098547774</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.729698181067235</v>
+        <v>-4.770315273707233</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.762827798159358</v>
+        <v>1.746580961103359</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6037879623290182</v>
+        <v>0.5631708696890189</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.017336272297412</v>
+        <v>3.992966016713412</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.754288425302419</v>
+        <v>-4.794905517942417</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.753962878217995</v>
+        <v>1.737716041161996</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6037879623290182</v>
+        <v>0.5631708696890189</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.018307450050122</v>
+        <v>3.993937194466122</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.703250049295899</v>
+        <v>-4.743867141935897</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.775221133000359</v>
+        <v>1.75897429594436</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6037879623290182</v>
+        <v>0.5631708696890189</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.019150354429877</v>
+        <v>3.994780098845878</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.662110754429268</v>
+        <v>-4.702727847069266</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.810714949821157</v>
+        <v>1.794468112765158</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.644927257195649</v>
+        <v>0.6043101645556497</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.062872030224002</v>
+        <v>4.038501774640002</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.565475842410628</v>
+        <v>-4.606092935050626</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.665552910752547</v>
+        <v>1.649306073696548</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.741562169214289</v>
+        <v>0.7009450765742896</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.93703697355912</v>
+        <v>3.91266671797512</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.49643783146216</v>
+        <v>-4.537054924102158</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.696670159205899</v>
+        <v>1.680423322149899</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.810600180162757</v>
+        <v>0.7699830875227577</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.981961824202165</v>
+        <v>3.957591568618166</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.422888068417722</v>
+        <v>-4.46350516105772</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.710516883499756</v>
+        <v>1.694270046443757</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8841499432071951</v>
+        <v>0.8435328505671957</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.010518501104911</v>
+        <v>3.98614824552091</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.345789466875849</v>
+        <v>-4.386406559515847</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.740544034552935</v>
+        <v>1.724297197496936</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8841499432071951</v>
+        <v>0.8435328505671957</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.00970621154134</v>
+        <v>3.985335955957341</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.356174661765738</v>
+        <v>-4.396791754405736</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.746258735722052</v>
+        <v>1.730011898666053</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8737647483173058</v>
+        <v>0.8331476556773064</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.013343873732479</v>
+        <v>3.98897361814848</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735276</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.374762820487963</v>
+        <v>-4.415379913127961</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.809660478009587</v>
+        <v>1.793413640953588</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8551765895950805</v>
+        <v>0.8145594969550811</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.073027984275569</v>
+        <v>4.04865772869157</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.375061367183999</v>
+        <v>-4.415678459823997</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.806410070149471</v>
+        <v>1.790163233093472</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8548780428990446</v>
+        <v>0.8142609502590452</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.069717867076246</v>
+        <v>4.045347611492247</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.274238233493572</v>
+        <v>-4.31485532613357</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.851270218565034</v>
+        <v>1.835023381509034</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8673422583833984</v>
+        <v>0.826725165743399</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.081727291306249</v>
+        <v>4.05735703572225</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.083456872741165</v>
+        <v>-4.124073965381163</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.92771201634454</v>
+        <v>1.911465179288541</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.058123619135806</v>
+        <v>1.017506526495807</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.196325361236237</v>
+        <v>4.171955105652238</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.976493514891743</v>
+        <v>-4.017110607531741</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.950334205221905</v>
+        <v>1.934087368165906</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.116588227095607</v>
+        <v>1.075971134455608</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.211240971749715</v>
+        <v>4.186870716165715</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.921162926989981</v>
+        <v>-3.961780019629979</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.007433376994668</v>
+        <v>1.991186539938669</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.171918814997369</v>
+        <v>1.13130172235737</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.279406261102831</v>
+        <v>4.255036005518831</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.909108800077018</v>
+        <v>-3.949725892717016</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.005941595661291</v>
+        <v>1.989694758605292</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.183972941910332</v>
+        <v>1.143355849270333</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.280325305152046</v>
+        <v>4.255955049568046</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.950263919645239</v>
+        <v>-3.990881012285237</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.991360178018138</v>
+        <v>1.975113340962139</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.142817822342111</v>
+        <v>1.102200729702112</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.257512863595249</v>
+        <v>4.233142608011249</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.882215356953709</v>
+        <v>-3.922832449593707</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.031430628972633</v>
+        <v>2.015183791916634</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.210866385033641</v>
+        <v>1.170249292393642</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.311193027088049</v>
+        <v>4.28682277150405</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.11381575012321</v>
+        <v>-4.154432842763208</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.958993141878427</v>
+        <v>1.942746304822427</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.210866385033641</v>
+        <v>1.170249292393642</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.331395697261644</v>
+        <v>4.307025441677644</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.16386729565243</v>
+        <v>-4.204484388292428</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.922578759733621</v>
+        <v>1.906331922677622</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.210866385033641</v>
+        <v>1.170249292393642</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.315001933328526</v>
+        <v>4.290631677744527</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.338974128228875</v>
+        <v>-4.379591220868873</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.812787940296509</v>
+        <v>1.79654110324051</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.210866385033641</v>
+        <v>1.170249292393642</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.275253846921992</v>
+        <v>4.250883591337993</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.142873974798352</v>
+        <v>-4.18349106743835</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.898250620665659</v>
+        <v>1.882003783609659</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.406966538464164</v>
+        <v>1.366349445824165</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.399936557977246</v>
+        <v>4.375566302393247</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.989848582685068</v>
+        <v>-4.030465675325066</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.058631777083876</v>
+        <v>2.042384940027878</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.559991930577448</v>
+        <v>1.519374837937449</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.590922792818121</v>
+        <v>4.566552537234122</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.018155896558338</v>
+        <v>-4.058772989198336</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.234775076442861</v>
+        <v>2.218528239386862</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.559991930577448</v>
+        <v>1.519374837937449</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.778389017726414</v>
+        <v>4.754018762142413</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.18474912167186</v>
+        <v>-4.225366214311858</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.137540737751535</v>
+        <v>2.121293900695536</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.393398705463926</v>
+        <v>1.352781612823926</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.647836034012383</v>
+        <v>4.623465778428383</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.161713328310294</v>
+        <v>-4.202330420950292</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.150431457757879</v>
+        <v>2.13418462070188</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.393398705463926</v>
+        <v>1.352781612823926</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.651512436674101</v>
+        <v>4.627142181090101</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.132467347854598</v>
+        <v>-4.173084440494596</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.159747905063653</v>
+        <v>2.143501068007654</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.393398705463926</v>
+        <v>1.352781612823926</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.649130491797596</v>
+        <v>4.624760236213596</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.239392895732449</v>
+        <v>-4.280009988372447</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.114270925070148</v>
+        <v>2.098024088014149</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.286473157586074</v>
+        <v>1.245856064946075</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.58226840222852</v>
+        <v>4.55789814664452</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600700997</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.384411454239697</v>
+        <v>-4.425028546879695</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.057692303810482</v>
+        <v>2.041445466754483</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.141454599078826</v>
+        <v>1.100837506438826</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.496686069267406</v>
+        <v>4.472315813683405</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687009</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.502753220024415</v>
+        <v>-4.543370312664413</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.110286836754348</v>
+        <v>2.094039999698349</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.152140637641716</v>
+        <v>1.111523545001717</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.603028931662893</v>
+        <v>4.578658676078892</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790799</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.554163642345123</v>
+        <v>-4.594780734985121</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.087508364952004</v>
+        <v>2.071261527896005</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.152140637641716</v>
+        <v>1.111523545001717</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.600814628788831</v>
+        <v>4.576444373204832</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.633583093552875</v>
+        <v>-4.674200186192873</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.055643712543193</v>
+        <v>2.039396875487194</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.152140637641716</v>
+        <v>1.111523545001717</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.600717756863121</v>
+        <v>4.576347501279121</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298393</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.729046091470092</v>
+        <v>-4.76966318411009</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.017452406934349</v>
+        <v>2.00120556987835</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.152140637641716</v>
+        <v>1.111523545001717</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.600711650421164</v>
+        <v>4.576341394837164</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217995</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.664670180619377</v>
+        <v>-4.705287273259375</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.041299167837245</v>
+        <v>2.025052330781246</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.216516548492431</v>
+        <v>1.175899455852432</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.637433593494203</v>
+        <v>4.613063337910203</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353531</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.720039342751571</v>
+        <v>-4.760656435391569</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.024885320732094</v>
+        <v>2.008638483676095</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.216516548492431</v>
+        <v>1.175899455852432</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.643167411241929</v>
+        <v>4.61879715565793</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113274</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.765477122582398</v>
+        <v>-4.806094215222396</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.006248572142696</v>
+        <v>1.990001735086697</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.173671557814272</v>
+        <v>1.133054465174272</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.616998780177966</v>
+        <v>4.592628524593967</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113683</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.67727028843482</v>
+        <v>-4.717887381074818</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.061405698652046</v>
+        <v>2.045158861596047</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.173671557814272</v>
+        <v>1.133054465174272</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.636873173028285</v>
+        <v>4.612502917444286</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.571235293229511</v>
+        <v>-4.611852385869509</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.087520397258897</v>
+        <v>2.071273560202898</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.173671557814272</v>
+        <v>1.133054465174272</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.620573873553013</v>
+        <v>4.596203617969014</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.388023630096415</v>
+        <v>-4.428640722736414</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.163236011976181</v>
+        <v>2.146989174920182</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.173671557814272</v>
+        <v>1.133054465174272</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.623004823017059</v>
+        <v>4.598634567433059</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.316302183082565</v>
+        <v>-4.356919275722563</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.157715776629611</v>
+        <v>2.141468939573612</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.245393004828122</v>
+        <v>1.204775912188123</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.631828877073259</v>
+        <v>4.607458621489259</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.293929157474858</v>
+        <v>-4.334546250114856</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.113580732793865</v>
+        <v>2.097333895737866</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.256648755941024</v>
+        <v>1.216031663301024</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.585498073662172</v>
+        <v>4.561127818078171</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.326945453385603</v>
+        <v>-4.367562546025601</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.285572419314922</v>
+        <v>2.269325582258924</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.187211379274272</v>
+        <v>1.146594286634273</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.729033852547476</v>
+        <v>4.704663596963476</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883672</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.315417817735995</v>
+        <v>-4.356034910375993</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.282104699403015</v>
+        <v>2.265857862347016</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.246212037475635</v>
+        <v>1.205594944835635</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.756355473296543</v>
+        <v>4.731985217712542</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236292</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.412759319078363</v>
+        <v>-4.453376411718361</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.246836211387857</v>
+        <v>2.230589374331857</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.201791855310146</v>
+        <v>1.161174762670147</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.733371476519038</v>
+        <v>4.709001220935038</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.49861534841833</v>
+        <v>-4.539232441058328</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.213744881844708</v>
+        <v>2.197498044788709</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.159415786084011</v>
+        <v>1.118798693444012</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.709196917176195</v>
+        <v>4.684826661592195</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.507452145834449</v>
+        <v>-4.548069238474447</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.192629364698762</v>
+        <v>2.176382527642763</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.151973613442661</v>
+        <v>1.111356520802661</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.687150815411886</v>
+        <v>4.662780559827887</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.598834708399908</v>
+        <v>-4.639451801039906</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.166240850717628</v>
+        <v>2.149994013661629</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.115408728723316</v>
+        <v>1.074791636083317</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.675376395625329</v>
+        <v>4.651006140041329</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.587127990412902</v>
+        <v>-4.6277450830529</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.273051795736698</v>
+        <v>2.256804958680698</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.127115446710322</v>
+        <v>1.086498354070323</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.7845286842418</v>
+        <v>4.7601584286578</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.487464486329239</v>
+        <v>-4.528081578969237</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.315949536101567</v>
+        <v>2.299702699045568</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.190302529914009</v>
+        <v>1.14968543727401</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.825473272895417</v>
+        <v>4.801103017311418</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.497780584495591</v>
+        <v>-4.538397677135589</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.524727930113085</v>
+        <v>2.508481093057085</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.190302529914009</v>
+        <v>1.14968543727401</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.038378106173475</v>
+        <v>5.014007850589476</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.497686616478219</v>
+        <v>-4.538303709118217</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.523944184232124</v>
+        <v>2.507697347176125</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.190672391261327</v>
+        <v>1.150055298621327</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.037778689893956</v>
+        <v>5.013408434309955</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.504905440678063</v>
+        <v>-4.545522533318061</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.515288640496539</v>
+        <v>2.49904180344054</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.190672391261327</v>
+        <v>1.150055298621327</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.032010675838309</v>
+        <v>5.00764042025431</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.503957017560024</v>
+        <v>-4.544574110200022</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.515668009743755</v>
+        <v>2.499421172687756</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.190672391261327</v>
+        <v>1.150055298621327</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.032010675838309</v>
+        <v>5.00764042025431</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.661025475815649</v>
+        <v>-4.701642568455647</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.465568234422597</v>
+        <v>2.449321397366598</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.190672391261327</v>
+        <v>1.150055298621327</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.044738283819401</v>
+        <v>5.020368028235401</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.655033229026837</v>
+        <v>-4.695650321666835</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.46991113156251</v>
+        <v>2.453664294506511</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.190672391261327</v>
+        <v>1.150055298621327</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.046684282243789</v>
+        <v>5.022314026659789</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.566475267896069</v>
+        <v>-4.607092360536067</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.498988452032585</v>
+        <v>2.482741614976586</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.190672391261327</v>
+        <v>1.150055298621327</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.040338418261558</v>
+        <v>5.015968162677558</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.548716190392995</v>
+        <v>-4.589333283032993</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.505400760472811</v>
+        <v>2.489153923416811</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.190672391261327</v>
+        <v>1.150055298621327</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.039647095700554</v>
+        <v>5.015276840116554</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.449086039343928</v>
+        <v>-4.489703131983926</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.558035006801025</v>
+        <v>2.541788169745026</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.290302542310394</v>
+        <v>1.249685449670395</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.112207372238581</v>
+        <v>5.087837116654581</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.498485548032939</v>
+        <v>-4.539102640672937</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.727429468824146</v>
+        <v>2.711182631768148</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.300561375742139</v>
+        <v>1.25994428310214</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.307516937796354</v>
+        <v>5.283146682212355</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.291801074390563</v>
+        <v>-4.332418167030561</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.797291931383959</v>
+        <v>2.78104509432796</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.507245849384515</v>
+        <v>1.466628756744516</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.418716295084641</v>
+        <v>5.394346039500642</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.325957969388089</v>
+        <v>-4.366575062028087</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.785630687039053</v>
+        <v>2.769383849983055</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.423662079843703</v>
+        <v>1.383044987203703</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.370567547014259</v>
+        <v>5.34619729143026</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.782482115652378</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.233368490326632</v>
+        <v>-4.27398558296663</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.176163592653304</v>
+        <v>3.159916755597305</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.423662079843703</v>
+        <v>1.383044987203703</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.724064661003927</v>
+        <v>5.699694405419927</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108665</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.293257118150183</v>
+        <v>-4.333874210790181</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.156771253090987</v>
+        <v>3.140524416034988</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.409540165156238</v>
+        <v>1.368923072516238</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.720154623758551</v>
+        <v>5.695784368174551</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.804033687708811</v>
+        <v>3.76098834077383</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.922466024393564</v>
+        <v>4.84510381048591</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.293257118150183</v>
+        <v>-4.333874210790181</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.156771253090987</v>
+        <v>3.140524416034988</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.409540165156238</v>
+        <v>1.368923072516238</v>
       </c>
       <c r="G2092" t="n">
-        <v>4.915529821379931</v>
+        <v>4.838167607472278</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240919.xlsx
+++ b/tame_output/ON/bt/strategyON_20240919.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-595.0%</t>
+          <t>-585.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-62.2%</t>
+          <t>-58.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.7%</t>
+          <t>-321.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>-78.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.606424982612299</v>
+        <v>-2.60601862520295</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.166204636149566</v>
+        <v>2.166367179113306</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.223210633645739</v>
+        <v>1.223616991055088</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.943057433695677</v>
+        <v>3.943301248141287</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.682754960213205</v>
+        <v>-2.682348602803856</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.133784458002979</v>
+        <v>2.133947000966718</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.223210633645739</v>
+        <v>1.223616991055088</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.941169246589452</v>
+        <v>3.941413061035062</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.776418904890746</v>
+        <v>-2.776012547481397</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.091139109734825</v>
+        <v>2.091301652698564</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.129546688968198</v>
+        <v>1.129953046377547</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.87979110938579</v>
+        <v>3.880034923831399</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.937987330418002</v>
+        <v>-2.937580973008652</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.024945749734075</v>
+        <v>2.025108292697815</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.002763765170318</v>
+        <v>1.003170122579667</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.802155365317215</v>
+        <v>3.802399179762824</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.046287992288121</v>
+        <v>-3.045881634878772</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.994698891851946</v>
+        <v>1.994861434815685</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.002763765170318</v>
+        <v>1.003170122579667</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.815228772183133</v>
+        <v>3.815472586628743</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.064091964008865</v>
+        <v>-3.063685606599516</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.979582499946588</v>
+        <v>1.979745042910328</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.932229142265117</v>
+        <v>0.9326354996744661</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.764913195222952</v>
+        <v>3.765157009668562</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.091992751118338</v>
+        <v>-3.091586393708989</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.966946226229801</v>
+        <v>1.96710876919354</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8976322181221822</v>
+        <v>0.8980385755315313</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.742679081864194</v>
+        <v>3.742922896309803</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.214518853821232</v>
+        <v>-3.214112496411883</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.914700229125842</v>
+        <v>1.914862772089582</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7751061154192883</v>
+        <v>0.7755124728286374</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.665927864219656</v>
+        <v>3.666171678665266</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.44503335000682</v>
+        <v>-3.444626992597471</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.88920039024211</v>
+        <v>1.88936293320585</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5445916192336996</v>
+        <v>0.5449979766430487</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.594325126098806</v>
+        <v>3.594568940544416</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.793778435231264</v>
+        <v>-3.793372077821915</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.89001407515418</v>
+        <v>1.89017661811792</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4358436653148018</v>
+        <v>0.4362500227241509</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.669388072749315</v>
+        <v>3.669631887194925</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.947764853007405</v>
+        <v>-3.947358495598055</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.897399777189364</v>
+        <v>1.897562320153103</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4358436653148018</v>
+        <v>0.4362500227241509</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.738368341894954</v>
+        <v>3.738612156340564</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.152364287870413</v>
+        <v>-4.151957930461064</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.801611205364281</v>
+        <v>1.801773748328021</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4358436653148018</v>
+        <v>0.4362500227241509</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.724419544015075</v>
+        <v>3.724663358460685</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.404839441878138</v>
+        <v>-4.404433084468788</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.712491632816605</v>
+        <v>1.712654175780345</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4358436653148018</v>
+        <v>0.4362500227241509</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.736290033070489</v>
+        <v>3.736533847516099</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.69773519835755</v>
+        <v>-4.697328840948201</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.596543864743784</v>
+        <v>1.596706407707524</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4358436653148018</v>
+        <v>0.4362500227241509</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.737500567589433</v>
+        <v>3.737744382035043</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.884399326492358</v>
+        <v>-4.883992969083009</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.525999955717182</v>
+        <v>1.526162498680922</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4091046944902419</v>
+        <v>0.409511051899591</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.725578927322019</v>
+        <v>3.725822741767628</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.03042001340632</v>
+        <v>-5.030013655996971</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.462669533687787</v>
+        <v>1.462832076651527</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4000216026963849</v>
+        <v>0.4004279601057341</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.715206924981894</v>
+        <v>3.715450739427503</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.122134022515905</v>
+        <v>-5.121727665106556</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.588187986742997</v>
+        <v>1.588350529706736</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4000216026963849</v>
+        <v>0.4004279601057341</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.877410981680938</v>
+        <v>3.877654796126548</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.153785681575874</v>
+        <v>-5.153379324166526</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.570373961082824</v>
+        <v>1.570536504046563</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3948531454519447</v>
+        <v>0.3952595028612939</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.869156545298088</v>
+        <v>3.869400359743698</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.222851736148811</v>
+        <v>-5.222445378739462</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.55297695682214</v>
+        <v>1.553139499785879</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3324822679583347</v>
+        <v>0.3328886253676838</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.841963436370413</v>
+        <v>3.842207250816023</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.324827858397218</v>
+        <v>-5.32442150098787</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.521112146378679</v>
+        <v>1.521274689342419</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2305061457099271</v>
+        <v>0.2309125031192762</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.789703401477271</v>
+        <v>3.789947215922881</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.214821574919997</v>
+        <v>-5.214415217510648</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.557267547013743</v>
+        <v>1.557430089977482</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2537107176272023</v>
+        <v>0.2541170750365515</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.795779031871811</v>
+        <v>3.796022846317421</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.071761999179071</v>
+        <v>-5.071355641769722</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.618741388032088</v>
+        <v>1.618903930995828</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2617241442171816</v>
+        <v>0.2621305016265307</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.804837098547774</v>
+        <v>3.805080912993383</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.770315273707233</v>
+        <v>-4.769908916297885</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.746580961103359</v>
+        <v>1.746743504067098</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5631708696890189</v>
+        <v>0.563577227098368</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.992966016713412</v>
+        <v>3.993209831159021</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.794905517942417</v>
+        <v>-4.794499160533069</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.737716041161996</v>
+        <v>1.737878584125735</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5631708696890189</v>
+        <v>0.563577227098368</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.993937194466122</v>
+        <v>3.994181008911732</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.743867141935897</v>
+        <v>-4.743460784526548</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.75897429594436</v>
+        <v>1.759136838908099</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5631708696890189</v>
+        <v>0.563577227098368</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.994780098845878</v>
+        <v>3.995023913291488</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.702727847069266</v>
+        <v>-4.702321489659917</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.794468112765158</v>
+        <v>1.794630655728897</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6043101645556497</v>
+        <v>0.6047165219649988</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.038501774640002</v>
+        <v>4.038745589085611</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.606092935050626</v>
+        <v>-4.605686577641277</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.649306073696548</v>
+        <v>1.649468616660287</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7009450765742896</v>
+        <v>0.7013514339836388</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.91266671797512</v>
+        <v>3.91291053242073</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.537054924102158</v>
+        <v>-4.53664856669281</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.680423322149899</v>
+        <v>1.680585865113639</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7699830875227577</v>
+        <v>0.7703894449321068</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.957591568618166</v>
+        <v>3.957835383063775</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.46350516105772</v>
+        <v>-4.372152232501848</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.694270046443757</v>
+        <v>1.730811217866106</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8435328505671957</v>
+        <v>0.9348857791230687</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.98614824552091</v>
+        <v>4.040960002654435</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.386406559515847</v>
+        <v>-4.295053630959975</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.724297197496936</v>
+        <v>1.760838368919285</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8435328505671957</v>
+        <v>0.9348857791230687</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.985335955957341</v>
+        <v>4.040147713090864</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.396791754405736</v>
+        <v>-4.305438825849865</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.730011898666053</v>
+        <v>1.766553070088401</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8331476556773064</v>
+        <v>0.9245005842331794</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.98897361814848</v>
+        <v>4.043785375282003</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735276</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.415379913127961</v>
+        <v>-4.32402698457209</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.793413640953588</v>
+        <v>1.829954812375937</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8145594969550811</v>
+        <v>0.9059124255109541</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.04865772869157</v>
+        <v>4.103469485825093</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.415678459823997</v>
+        <v>-4.324325531268125</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.790163233093472</v>
+        <v>1.826704404515821</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8142609502590452</v>
+        <v>0.9056138788149182</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.045347611492247</v>
+        <v>4.10015936862577</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108851</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.31485532613357</v>
+        <v>-4.223502397577698</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.835023381509034</v>
+        <v>1.871564552931383</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.826725165743399</v>
+        <v>0.918078094299272</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.05735703572225</v>
+        <v>4.112168792855774</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812146</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.124073965381163</v>
+        <v>-4.03272103682529</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.911465179288541</v>
+        <v>1.94800635071089</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.017506526495807</v>
+        <v>1.108859455051679</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.171955105652238</v>
+        <v>4.226766862785762</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.017110607531741</v>
+        <v>-3.925757678975868</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.934087368165906</v>
+        <v>1.970628539588255</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.075971134455608</v>
+        <v>1.167324063011481</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.186870716165715</v>
+        <v>4.241682473299239</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.961780019629979</v>
+        <v>-3.870427091074106</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.991186539938669</v>
+        <v>2.027727711361018</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.13130172235737</v>
+        <v>1.222654650913243</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.255036005518831</v>
+        <v>4.309847762652354</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.949725892717016</v>
+        <v>-3.858372964161144</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.989694758605292</v>
+        <v>2.026235930027641</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.143355849270333</v>
+        <v>1.234708777826206</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.255955049568046</v>
+        <v>4.31076680670157</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.990881012285237</v>
+        <v>-3.899528083729364</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.975113340962139</v>
+        <v>2.011654512384489</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.102200729702112</v>
+        <v>1.193553658257985</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.233142608011249</v>
+        <v>4.287954365144773</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.922832449593707</v>
+        <v>-3.831479521037835</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.015183791916634</v>
+        <v>2.051724963338983</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.170249292393642</v>
+        <v>1.261602220949515</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.28682277150405</v>
+        <v>4.341634528637574</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013421</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.154432842763208</v>
+        <v>-4.063079914207336</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.942746304822427</v>
+        <v>1.979287476244776</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.170249292393642</v>
+        <v>1.261602220949515</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.307025441677644</v>
+        <v>4.361837198811168</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.204484388292428</v>
+        <v>-4.113131459736556</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.906331922677622</v>
+        <v>1.942873094099971</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.170249292393642</v>
+        <v>1.261602220949515</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.290631677744527</v>
+        <v>4.34544343487805</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.379591220868873</v>
+        <v>-4.288238292313</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.79654110324051</v>
+        <v>1.833082274662859</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.170249292393642</v>
+        <v>1.261602220949515</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.250883591337993</v>
+        <v>4.305695348471517</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.18349106743835</v>
+        <v>-4.092138138882477</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.882003783609659</v>
+        <v>1.918544955032009</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.366349445824165</v>
+        <v>1.457702374380037</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.375566302393247</v>
+        <v>4.43037805952677</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395084</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.030465675325066</v>
+        <v>-3.939112746769193</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.042384940027878</v>
+        <v>2.078926111450227</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.519374837937449</v>
+        <v>1.610727766493322</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.566552537234122</v>
+        <v>4.621364294367645</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791146</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.058772989198336</v>
+        <v>-3.967420060642463</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.218528239386862</v>
+        <v>2.255069410809211</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.519374837937449</v>
+        <v>1.610727766493322</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.754018762142413</v>
+        <v>4.808830519275937</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.225366214311858</v>
+        <v>-4.134013285755985</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.121293900695536</v>
+        <v>2.157835072117885</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.352781612823926</v>
+        <v>1.444134541379799</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.623465778428383</v>
+        <v>4.678277535561907</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.202330420950292</v>
+        <v>-4.11097749239442</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.13418462070188</v>
+        <v>2.170725792124229</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.352781612823926</v>
+        <v>1.444134541379799</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.627142181090101</v>
+        <v>4.681953938223625</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399466</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.173084440494596</v>
+        <v>-4.081731511938723</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.143501068007654</v>
+        <v>2.180042239430003</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.352781612823926</v>
+        <v>1.444134541379799</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.624760236213596</v>
+        <v>4.679571993347119</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.280009988372447</v>
+        <v>-4.188657059816574</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.098024088014149</v>
+        <v>2.134565259436497</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.245856064946075</v>
+        <v>1.337208993501948</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.55789814664452</v>
+        <v>4.612709903778044</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700997</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.425028546879695</v>
+        <v>-4.333675618323823</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.041445466754483</v>
+        <v>2.077986638176832</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.100837506438826</v>
+        <v>1.192190434994699</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.472315813683405</v>
+        <v>4.527127570816929</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687009</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.543370312664413</v>
+        <v>-4.45201738410854</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.094039999698349</v>
+        <v>2.130581171120698</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.111523545001717</v>
+        <v>1.202876473557589</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.578658676078892</v>
+        <v>4.633470433212416</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790799</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.594780734985121</v>
+        <v>-4.503427806429248</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.071261527896005</v>
+        <v>2.107802699318354</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.111523545001717</v>
+        <v>1.202876473557589</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.576444373204832</v>
+        <v>4.631256130338356</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437326</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.674200186192873</v>
+        <v>-4.582847257637</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.039396875487194</v>
+        <v>2.075938046909543</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.111523545001717</v>
+        <v>1.202876473557589</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.576347501279121</v>
+        <v>4.631159258412644</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298393</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.76966318411009</v>
+        <v>-4.678310255554218</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.00120556987835</v>
+        <v>2.037746741300698</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.111523545001717</v>
+        <v>1.202876473557589</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.576341394837164</v>
+        <v>4.631153151970688</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217995</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.705287273259375</v>
+        <v>-4.613934344703503</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.025052330781246</v>
+        <v>2.061593502203595</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.175899455852432</v>
+        <v>1.267252384408305</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.613063337910203</v>
+        <v>4.667875095043727</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353531</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.760656435391569</v>
+        <v>-4.669303506835696</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.008638483676095</v>
+        <v>2.045179655098444</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.175899455852432</v>
+        <v>1.267252384408305</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.61879715565793</v>
+        <v>4.673608912791454</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113274</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.806094215222396</v>
+        <v>-4.714741286666523</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.990001735086697</v>
+        <v>2.026542906509046</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.133054465174272</v>
+        <v>1.224407393730145</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.592628524593967</v>
+        <v>4.647440281727491</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113683</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.717887381074818</v>
+        <v>-4.626534452518945</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.045158861596047</v>
+        <v>2.081700033018396</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.133054465174272</v>
+        <v>1.224407393730145</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.612502917444286</v>
+        <v>4.667314674577809</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.611852385869509</v>
+        <v>-4.520499457313636</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.071273560202898</v>
+        <v>2.107814731625248</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.133054465174272</v>
+        <v>1.224407393730145</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.596203617969014</v>
+        <v>4.651015375102537</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.428640722736414</v>
+        <v>-4.337287794180541</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.146989174920182</v>
+        <v>2.183530346342531</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.133054465174272</v>
+        <v>1.224407393730145</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.598634567433059</v>
+        <v>4.653446324566582</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.356919275722563</v>
+        <v>-4.26556634716669</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.141468939573612</v>
+        <v>2.178010110995961</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.204775912188123</v>
+        <v>1.296128840743996</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.607458621489259</v>
+        <v>4.662270378622783</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.334546250114856</v>
+        <v>-4.243193321558984</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.097333895737866</v>
+        <v>2.133875067160215</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.216031663301024</v>
+        <v>1.307384591856897</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.561127818078171</v>
+        <v>4.615939575211695</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.367562546025601</v>
+        <v>-4.276209617469728</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.269325582258924</v>
+        <v>2.305866753681273</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.146594286634273</v>
+        <v>1.237947215190146</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.704663596963476</v>
+        <v>4.759475354097</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883672</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.356034910375993</v>
+        <v>-4.26468198182012</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.265857862347016</v>
+        <v>2.302399033769365</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.205594944835635</v>
+        <v>1.296947873391508</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.731985217712542</v>
+        <v>4.786796974846066</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236292</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.453376411718361</v>
+        <v>-4.362023483162488</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.230589374331857</v>
+        <v>2.267130545754206</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.161174762670147</v>
+        <v>1.25252769122602</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.709001220935038</v>
+        <v>4.763812978068562</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.539232441058328</v>
+        <v>-4.447879512502455</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.197498044788709</v>
+        <v>2.234039216211058</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.118798693444012</v>
+        <v>1.210151621999885</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.684826661592195</v>
+        <v>4.739638418725719</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.548069238474447</v>
+        <v>-4.456716309918574</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.176382527642763</v>
+        <v>2.212923699065112</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.111356520802661</v>
+        <v>1.202709449358534</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.662780559827887</v>
+        <v>4.71759231696141</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.639451801039906</v>
+        <v>-4.548098872484033</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.149994013661629</v>
+        <v>2.186535185083978</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.074791636083317</v>
+        <v>1.166144564639189</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.651006140041329</v>
+        <v>4.705817897174853</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.6277450830529</v>
+        <v>-4.536392154497027</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.256804958680698</v>
+        <v>2.293346130103048</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.086498354070323</v>
+        <v>1.177851282626196</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.7601584286578</v>
+        <v>4.814970185791324</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.528081578969237</v>
+        <v>-4.436728650413365</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.299702699045568</v>
+        <v>2.336243870467917</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.14968543727401</v>
+        <v>1.241038365829882</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.801103017311418</v>
+        <v>4.85591477444494</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.538397677135589</v>
+        <v>-4.447044748579716</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.508481093057085</v>
+        <v>2.545022264479435</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.14968543727401</v>
+        <v>1.241038365829882</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.014007850589476</v>
+        <v>5.068819607722999</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.538303709118217</v>
+        <v>-4.446950780562344</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.507697347176125</v>
+        <v>2.544238518598473</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.150055298621327</v>
+        <v>1.2414082271772</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.013408434309955</v>
+        <v>5.068220191443479</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988013</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.545522533318061</v>
+        <v>-4.454169604762188</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.49904180344054</v>
+        <v>2.53558297486289</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.150055298621327</v>
+        <v>1.2414082271772</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.00764042025431</v>
+        <v>5.062452177387833</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740919</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.544574110200022</v>
+        <v>-4.45322118164415</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.499421172687756</v>
+        <v>2.535962344110105</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.150055298621327</v>
+        <v>1.2414082271772</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.00764042025431</v>
+        <v>5.062452177387833</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.701642568455647</v>
+        <v>-4.610289639899774</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.449321397366598</v>
+        <v>2.485862568788948</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.150055298621327</v>
+        <v>1.2414082271772</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.020368028235401</v>
+        <v>5.075179785368925</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.695650321666835</v>
+        <v>-4.604297393110962</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.453664294506511</v>
+        <v>2.490205465928859</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.150055298621327</v>
+        <v>1.2414082271772</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.022314026659789</v>
+        <v>5.077125783793313</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.607092360536067</v>
+        <v>-4.515739431980195</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.482741614976586</v>
+        <v>2.519282786398936</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.150055298621327</v>
+        <v>1.2414082271772</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.015968162677558</v>
+        <v>5.070779919811081</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383087</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.589333283032993</v>
+        <v>-4.497980354477121</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.489153923416811</v>
+        <v>2.525695094839161</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.150055298621327</v>
+        <v>1.2414082271772</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.015276840116554</v>
+        <v>5.070088597250077</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.489703131983926</v>
+        <v>-4.398350203428053</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.541788169745026</v>
+        <v>2.578329341167374</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.249685449670395</v>
+        <v>1.341038378226268</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.087837116654581</v>
+        <v>5.142648873788104</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.539102640672937</v>
+        <v>-4.447749712117064</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.711182631768148</v>
+        <v>2.747723803190497</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.25994428310214</v>
+        <v>1.351297211658013</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.283146682212355</v>
+        <v>5.337958439345878</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.332418167030561</v>
+        <v>-4.241065238474688</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.78104509432796</v>
+        <v>2.817586265750309</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.466628756744516</v>
+        <v>1.557981685300388</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.394346039500642</v>
+        <v>5.449157796634165</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.366575062028087</v>
+        <v>-4.275222133472214</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.769383849983055</v>
+        <v>2.805925021405404</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.383044987203703</v>
+        <v>1.474397915759576</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.34619729143026</v>
+        <v>5.401009048563783</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652378</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.27398558296663</v>
+        <v>-4.182632654410757</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.159916755597305</v>
+        <v>3.196457927019654</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.383044987203703</v>
+        <v>1.474397915759576</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.699694405419927</v>
+        <v>5.754506162553451</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108665</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.333874210790181</v>
+        <v>-4.242521282234308</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.140524416034988</v>
+        <v>3.177065587457337</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.368923072516238</v>
+        <v>1.460276001072111</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.695784368174551</v>
+        <v>5.750596125308075</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,19 +49661,19 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.76098834077383</v>
+        <v>3.760988340773833</v>
       </c>
       <c r="C2092" t="n">
         <v>4.84510381048591</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.333874210790181</v>
+        <v>-4.242521282234308</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.140524416034988</v>
+        <v>3.177065587457337</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.368923072516238</v>
+        <v>1.460276001072111</v>
       </c>
       <c r="G2092" t="n">
         <v>4.838167607472278</v>

--- a/tame_output/ON/bt/strategyON_20240919.xlsx
+++ b/tame_output/ON/bt/strategyON_20240919.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>111.9%</t>
+          <t>112.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>172.9%</t>
+          <t>173.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-70.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-585.8%</t>
+          <t>-581.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-58.5%</t>
+          <t>-64.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.7%</t>
+          <t>-322.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-73.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.0%</t>
         </is>
       </c>
     </row>
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.60601862520295</v>
+        <v>-2.5658078899723</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.166367179113306</v>
+        <v>2.182451473205566</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.223616991055088</v>
+        <v>1.263827726285738</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.943301248141287</v>
+        <v>3.967427689279677</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.682348602803856</v>
+        <v>-2.642137867573206</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.133947000966718</v>
+        <v>2.150031295058978</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.223616991055088</v>
+        <v>1.263827726285738</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.941413061035062</v>
+        <v>3.965539502173452</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.776012547481397</v>
+        <v>-2.735801812250747</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.091301652698564</v>
+        <v>2.107385946790824</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.129953046377547</v>
+        <v>1.170163781608197</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.880034923831399</v>
+        <v>3.904161364969789</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.937580973008652</v>
+        <v>-2.897370237778002</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.025108292697815</v>
+        <v>2.041192586790075</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.003170122579667</v>
+        <v>1.043380857810317</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.802399179762824</v>
+        <v>3.826525620901214</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.045881634878772</v>
+        <v>-3.005670899648122</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.994861434815685</v>
+        <v>2.010945728907945</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.003170122579667</v>
+        <v>1.043380857810317</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.815472586628743</v>
+        <v>3.839599027767133</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.063685606599516</v>
+        <v>-3.023474871368866</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.979745042910328</v>
+        <v>1.995829337002588</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9326354996744661</v>
+        <v>0.9728462349051163</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.765157009668562</v>
+        <v>3.789283450806952</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.091586393708989</v>
+        <v>-3.051375658478339</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.96710876919354</v>
+        <v>1.983193063285801</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8980385755315313</v>
+        <v>0.9382493107621815</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.742922896309803</v>
+        <v>3.767049337448193</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.214112496411883</v>
+        <v>-3.173901761181233</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.914862772089582</v>
+        <v>1.930947066181842</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7755124728286374</v>
+        <v>0.8157232080592877</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.666171678665266</v>
+        <v>3.690298119803656</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.444626992597471</v>
+        <v>-3.404416257366822</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.88936293320585</v>
+        <v>1.90544722729811</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5449979766430487</v>
+        <v>0.5852087118736989</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.594568940544416</v>
+        <v>3.618695381682806</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.793372077821915</v>
+        <v>-3.753161342591265</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.89017661811792</v>
+        <v>1.906260912210179</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4362500227241509</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.669631887194925</v>
+        <v>3.693758328333314</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.947358495598055</v>
+        <v>-3.907147760367406</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.897562320153103</v>
+        <v>1.913646614245363</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4362500227241509</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.738612156340564</v>
+        <v>3.762738597478954</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.151957930461064</v>
+        <v>-4.111747195230414</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.801773748328021</v>
+        <v>1.81785804242028</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4362500227241509</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.724663358460685</v>
+        <v>3.748789799599075</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.404433084468788</v>
+        <v>-4.364222349238139</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.712654175780345</v>
+        <v>1.728738469872605</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4362500227241509</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.736533847516099</v>
+        <v>3.760660288654489</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.697328840948201</v>
+        <v>-4.657118105717551</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.596706407707524</v>
+        <v>1.612790701799784</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4362500227241509</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.737744382035043</v>
+        <v>3.761870823173433</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.883992969083009</v>
+        <v>-4.843782233852359</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.526162498680922</v>
+        <v>1.542246792773182</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.409511051899591</v>
+        <v>0.4497217871302412</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.725822741767628</v>
+        <v>3.749949182906018</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.030013655996971</v>
+        <v>-4.989802920766321</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.462832076651527</v>
+        <v>1.478916370743786</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4004279601057341</v>
+        <v>0.4406386953363843</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.715450739427503</v>
+        <v>3.739577180565893</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.121727665106556</v>
+        <v>-5.081516929875907</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.588350529706736</v>
+        <v>1.604434823798996</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4004279601057341</v>
+        <v>0.4406386953363843</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.877654796126548</v>
+        <v>3.901781237264938</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.153379324166526</v>
+        <v>-5.113168588935876</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.570536504046563</v>
+        <v>1.586620798138823</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3952595028612939</v>
+        <v>0.4354702380919441</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.869400359743698</v>
+        <v>3.893526800882088</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.222445378739462</v>
+        <v>-5.182234643508813</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.553139499785879</v>
+        <v>1.569223793878139</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3328886253676838</v>
+        <v>0.373099360598334</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.842207250816023</v>
+        <v>3.866333691954413</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.32442150098787</v>
+        <v>-5.28421076575722</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.521274689342419</v>
+        <v>1.537358983434678</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2309125031192762</v>
+        <v>0.2711232383499265</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.789947215922881</v>
+        <v>3.814073657061271</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.214415217510648</v>
+        <v>-5.174204482279999</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.557430089977482</v>
+        <v>1.573514384069743</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2541170750365515</v>
+        <v>0.2943278102672017</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.796022846317421</v>
+        <v>3.820149287455811</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.071355641769722</v>
+        <v>-5.031144906539073</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.618903930995828</v>
+        <v>1.634988225088087</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2621305016265307</v>
+        <v>0.302341236857181</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.805080912993383</v>
+        <v>3.829207354131773</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.769908916297885</v>
+        <v>-4.729698181067235</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.746743504067098</v>
+        <v>1.762827798159358</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.563577227098368</v>
+        <v>0.6037879623290182</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.993209831159021</v>
+        <v>4.017336272297412</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.794499160533069</v>
+        <v>-4.754288425302419</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.737878584125735</v>
+        <v>1.753962878217995</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.563577227098368</v>
+        <v>0.6037879623290182</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.994181008911732</v>
+        <v>4.018307450050122</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.743460784526548</v>
+        <v>-4.703250049295899</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.759136838908099</v>
+        <v>1.775221133000359</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.563577227098368</v>
+        <v>0.6037879623290182</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.995023913291488</v>
+        <v>4.019150354429877</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.702321489659917</v>
+        <v>-4.662110754429268</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.794630655728897</v>
+        <v>1.810714949821157</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6047165219649988</v>
+        <v>0.644927257195649</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.038745589085611</v>
+        <v>4.062872030224002</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.605686577641277</v>
+        <v>-4.565475842410628</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.649468616660287</v>
+        <v>1.665552910752547</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7013514339836388</v>
+        <v>0.741562169214289</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.91291053242073</v>
+        <v>3.93703697355912</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.53664856669281</v>
+        <v>-4.49643783146216</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.680585865113639</v>
+        <v>1.696670159205899</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7703894449321068</v>
+        <v>0.810600180162757</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.957835383063775</v>
+        <v>3.981961824202165</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.372152232501848</v>
+        <v>-4.331941497271198</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.730811217866106</v>
+        <v>1.746895511958366</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9348857791230687</v>
+        <v>0.9750965143537189</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.040960002654435</v>
+        <v>4.065086443792825</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.295053630959975</v>
+        <v>-4.254842895729325</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.760838368919285</v>
+        <v>1.776922663011545</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9348857791230687</v>
+        <v>0.9750965143537189</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.040147713090864</v>
+        <v>4.064274154229254</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.305438825849865</v>
+        <v>-4.265228090619215</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.766553070088401</v>
+        <v>1.782637364180661</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9245005842331794</v>
+        <v>0.9647113194638296</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.043785375282003</v>
+        <v>4.067911816420393</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.32402698457209</v>
+        <v>-4.28381624934144</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.829954812375937</v>
+        <v>1.846039106468196</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9059124255109541</v>
+        <v>0.9461231607416043</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.103469485825093</v>
+        <v>4.127595926963483</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.324325531268125</v>
+        <v>-4.284114796037476</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.826704404515821</v>
+        <v>1.842788698608081</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9056138788149182</v>
+        <v>0.9458246140455684</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.10015936862577</v>
+        <v>4.12428580976416</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.223502397577698</v>
+        <v>-4.183291662347048</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.871564552931383</v>
+        <v>1.887648847023643</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.918078094299272</v>
+        <v>0.9582888295299222</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.112168792855774</v>
+        <v>4.136295233994164</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.03272103682529</v>
+        <v>-3.992510301594641</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.94800635071089</v>
+        <v>1.964090644803149</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.108859455051679</v>
+        <v>1.149070190282329</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.226766862785762</v>
+        <v>4.250893303924151</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.925757678975868</v>
+        <v>-3.885546943745219</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.970628539588255</v>
+        <v>1.986712833680515</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.167324063011481</v>
+        <v>1.207534798242131</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.241682473299239</v>
+        <v>4.265808914437629</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.870427091074106</v>
+        <v>-3.830216355843457</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.027727711361018</v>
+        <v>2.043812005453278</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.222654650913243</v>
+        <v>1.262865386143893</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.309847762652354</v>
+        <v>4.333974203790745</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.858372964161144</v>
+        <v>-3.818162228930494</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.026235930027641</v>
+        <v>2.042320224119901</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.234708777826206</v>
+        <v>1.274919513056856</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.31076680670157</v>
+        <v>4.33489324783996</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.899528083729364</v>
+        <v>-3.859317348498715</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.011654512384489</v>
+        <v>2.027738806476748</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.193553658257985</v>
+        <v>1.233764393488635</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.287954365144773</v>
+        <v>4.312080806283164</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.831479521037835</v>
+        <v>-3.791268785807185</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.051724963338983</v>
+        <v>2.067809257431243</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.261602220949515</v>
+        <v>1.301812956180165</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.341634528637574</v>
+        <v>4.365760969775963</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.063079914207336</v>
+        <v>-4.022869178976686</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.979287476244776</v>
+        <v>1.995371770337036</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.261602220949515</v>
+        <v>1.301812956180165</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.361837198811168</v>
+        <v>4.385963639949558</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.113131459736556</v>
+        <v>-4.072920724505906</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.942873094099971</v>
+        <v>1.958957388192231</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.261602220949515</v>
+        <v>1.301812956180165</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.34544343487805</v>
+        <v>4.36956987601644</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.288238292313</v>
+        <v>-4.24802755708235</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.833082274662859</v>
+        <v>1.849166568755119</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.261602220949515</v>
+        <v>1.301812956180165</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.305695348471517</v>
+        <v>4.329821789609906</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.092138138882477</v>
+        <v>-4.051927403651828</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.918544955032009</v>
+        <v>1.934629249124268</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.457702374380037</v>
+        <v>1.497913109610688</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.43037805952677</v>
+        <v>4.45450450066516</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.939112746769193</v>
+        <v>-3.898902011538544</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.078926111450227</v>
+        <v>2.095010405542487</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.610727766493322</v>
+        <v>1.650938501723972</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.621364294367645</v>
+        <v>4.645490735506035</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.967420060642463</v>
+        <v>-3.927209325411813</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.255069410809211</v>
+        <v>2.271153704901471</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.610727766493322</v>
+        <v>1.650938501723972</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.808830519275937</v>
+        <v>4.832956960414328</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.134013285755985</v>
+        <v>-4.093802550525336</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.157835072117885</v>
+        <v>2.173919366210145</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.444134541379799</v>
+        <v>1.484345276610449</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.678277535561907</v>
+        <v>4.702403976700297</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.11097749239442</v>
+        <v>-4.07076675716377</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.170725792124229</v>
+        <v>2.186810086216489</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.444134541379799</v>
+        <v>1.484345276610449</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.681953938223625</v>
+        <v>4.706080379362015</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399468</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.081731511938723</v>
+        <v>-4.041520776708073</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.180042239430003</v>
+        <v>2.196126533522263</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.444134541379799</v>
+        <v>1.484345276610449</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.679571993347119</v>
+        <v>4.70369843448551</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.699404642256369</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.188657059816574</v>
+        <v>-4.148446324585924</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.134565259436497</v>
+        <v>2.150649553528758</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.337208993501948</v>
+        <v>1.377419728732598</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.612709903778044</v>
+        <v>4.636836344916434</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.333675618323823</v>
+        <v>-4.293464883093173</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.077986638176832</v>
+        <v>2.094070932269092</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.192190434994699</v>
+        <v>1.232401170225349</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.527127570816929</v>
+        <v>4.55125401195532</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687011</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.45201738410854</v>
+        <v>-4.41180664887789</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.130581171120698</v>
+        <v>2.146665465212958</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.202876473557589</v>
+        <v>1.24308720878824</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.633470433212416</v>
+        <v>4.657596874350807</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790801</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.503427806429248</v>
+        <v>-4.463217071198598</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.107802699318354</v>
+        <v>2.123886993410614</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.202876473557589</v>
+        <v>1.24308720878824</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.631256130338356</v>
+        <v>4.655382571476745</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.582847257637</v>
+        <v>-4.54263652240635</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.075938046909543</v>
+        <v>2.092022341001803</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.202876473557589</v>
+        <v>1.24308720878824</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.631159258412644</v>
+        <v>4.655285699551035</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.678310255554218</v>
+        <v>-4.638099520323568</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.037746741300698</v>
+        <v>2.053831035392959</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.202876473557589</v>
+        <v>1.24308720878824</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.631153151970688</v>
+        <v>4.655279593109078</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.613934344703503</v>
+        <v>-4.573723609472853</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.061593502203595</v>
+        <v>2.077677796295855</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.267252384408305</v>
+        <v>1.307463119638955</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.667875095043727</v>
+        <v>4.692001536182118</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.669303506835696</v>
+        <v>-4.629092771605047</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.045179655098444</v>
+        <v>2.061263949190704</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.267252384408305</v>
+        <v>1.307463119638955</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.673608912791454</v>
+        <v>4.697735353929844</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.714741286666523</v>
+        <v>-4.674530551435874</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.026542906509046</v>
+        <v>2.042627200601306</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.224407393730145</v>
+        <v>1.264618128960795</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.647440281727491</v>
+        <v>4.67156672286588</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.626534452518945</v>
+        <v>-4.586323717288296</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.081700033018396</v>
+        <v>2.097784327110656</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.224407393730145</v>
+        <v>1.264618128960795</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.667314674577809</v>
+        <v>4.691441115716199</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.520499457313636</v>
+        <v>-4.480288722082986</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.107814731625248</v>
+        <v>2.123899025717507</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.224407393730145</v>
+        <v>1.264618128960795</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.651015375102537</v>
+        <v>4.675141816240927</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.337287794180541</v>
+        <v>-4.297077058949891</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.183530346342531</v>
+        <v>2.199614640434791</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.224407393730145</v>
+        <v>1.264618128960795</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.653446324566582</v>
+        <v>4.677572765704973</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.26556634716669</v>
+        <v>-4.22535561193604</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.178010110995961</v>
+        <v>2.194094405088221</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.296128840743996</v>
+        <v>1.336339575974646</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.662270378622783</v>
+        <v>4.686396819761173</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.243193321558984</v>
+        <v>-4.202982586328334</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.133875067160215</v>
+        <v>2.149959361252475</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.307384591856897</v>
+        <v>1.347595327087547</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.615939575211695</v>
+        <v>4.640066016350086</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.276209617469728</v>
+        <v>-4.235998882239079</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.305866753681273</v>
+        <v>2.321951047773533</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.237947215190146</v>
+        <v>1.278157950420796</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.759475354097</v>
+        <v>4.78360179523539</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.26468198182012</v>
+        <v>-4.22447124658947</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.302399033769365</v>
+        <v>2.318483327861625</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.296947873391508</v>
+        <v>1.337158608622158</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.786796974846066</v>
+        <v>4.810923415984456</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.362023483162488</v>
+        <v>-4.321812747931839</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.267130545754206</v>
+        <v>2.283214839846466</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.25252769122602</v>
+        <v>1.29273842645667</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.763812978068562</v>
+        <v>4.787939419206952</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.447879512502455</v>
+        <v>-4.407668777271805</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.234039216211058</v>
+        <v>2.250123510303318</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.210151621999885</v>
+        <v>1.250362357230535</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.739638418725719</v>
+        <v>4.763764859864109</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.456716309918574</v>
+        <v>-4.416505574687925</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.212923699065112</v>
+        <v>2.229007993157372</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.202709449358534</v>
+        <v>1.242920184589184</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.71759231696141</v>
+        <v>4.7417187580998</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.548098872484033</v>
+        <v>-4.507888137253383</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.186535185083978</v>
+        <v>2.202619479176238</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.166144564639189</v>
+        <v>1.206355299869839</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.705817897174853</v>
+        <v>4.729944338313243</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.033297452870161</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.536392154497027</v>
+        <v>-4.496181419266377</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.293346130103048</v>
+        <v>2.234468460849862</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.177851282626196</v>
+        <v>1.218062017856846</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.814970185791324</v>
+        <v>4.764134663584269</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.036329791601566</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.436728650413365</v>
+        <v>-4.396517915182715</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.336243870467917</v>
+        <v>2.277366201214732</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.241038365829882</v>
+        <v>1.281249101060532</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.85591477444494</v>
+        <v>4.805079252237886</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.249234624879625</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.447044748579716</v>
+        <v>-4.406834013349067</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.545022264479435</v>
+        <v>2.48614459522625</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.241038365829882</v>
+        <v>1.281249101060532</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.068819607722999</v>
+        <v>5.017984085515945</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.248413291791715</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.446950780562344</v>
+        <v>-4.406740045331694</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.544238518598473</v>
+        <v>2.485360849345289</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.2414082271772</v>
+        <v>1.28161896240785</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.068220191443479</v>
+        <v>5.017384669236425</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.242645277736068</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.454169604762188</v>
+        <v>-4.413958869531538</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.53558297486289</v>
+        <v>2.476705305609705</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.2414082271772</v>
+        <v>1.28161896240785</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.062452177387833</v>
+        <v>5.011616655180779</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.242645277736068</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.45322118164415</v>
+        <v>-4.4130104464135</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.535962344110105</v>
+        <v>2.47708467485692</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.2414082271772</v>
+        <v>1.28161896240785</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.062452177387833</v>
+        <v>5.011616655180779</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.25537288571716</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.610289639899774</v>
+        <v>-4.570078904669124</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.485862568788948</v>
+        <v>2.426984899535763</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.2414082271772</v>
+        <v>1.28161896240785</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.075179785368925</v>
+        <v>5.024344263161871</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.257318884141548</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.604297393110962</v>
+        <v>-4.564086657880313</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.490205465928859</v>
+        <v>2.431327796675675</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.2414082271772</v>
+        <v>1.28161896240785</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.077125783793313</v>
+        <v>5.026290261586259</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.250973020159317</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.515739431980195</v>
+        <v>-4.475528696749545</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.519282786398936</v>
+        <v>2.460405117145751</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.2414082271772</v>
+        <v>1.28161896240785</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.070779919811081</v>
+        <v>5.019944397604028</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.250281697598313</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.497980354477121</v>
+        <v>-4.457769619246471</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.525695094839161</v>
+        <v>2.466817425585976</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.2414082271772</v>
+        <v>1.28161896240785</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.070088597250077</v>
+        <v>5.019253075043023</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.263063883506899</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.398350203428053</v>
+        <v>-4.358139468197403</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.578329341167374</v>
+        <v>2.51945167191419</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.341038378226268</v>
+        <v>1.381249113456918</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.142648873788104</v>
+        <v>5.091813351581051</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.452218149005626</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.447749712117064</v>
+        <v>-4.407538976886414</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.747723803190497</v>
+        <v>2.688846133937312</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.351297211658013</v>
+        <v>1.391507946888663</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.337958439345878</v>
+        <v>5.287122917138824</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.439406822108488</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.241065238474688</v>
+        <v>-4.200854503244038</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.817586265750309</v>
+        <v>2.758708596497125</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.557981685300388</v>
+        <v>1.598192420531038</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.449157796634165</v>
+        <v>5.398322274427112</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.441408335762593</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.275222133472214</v>
+        <v>-4.235011398241564</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.805925021405404</v>
+        <v>2.747047352152219</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.474397915759576</v>
+        <v>1.514608650990226</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.401009048563783</v>
+        <v>5.350173526356729</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.79490544975226</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.182632654410757</v>
+        <v>-4.142421919180108</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.196457927019654</v>
+        <v>3.137580257766469</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.474397915759576</v>
+        <v>1.514608650990226</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.754506162553451</v>
+        <v>5.703670640346396</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108666</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.874430524664808</v>
+        <v>4.799468561319364</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.242521282234308</v>
+        <v>-4.202310547003658</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.177065587457337</v>
+        <v>3.118187918204153</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.460276001072111</v>
+        <v>1.500486736302761</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.750596125308075</v>
+        <v>5.699760603101021</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.760988340773833</v>
+        <v>3.787804892116936</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.84510381048591</v>
+        <v>4.847289909960391</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.242521282234308</v>
+        <v>-4.202310547003658</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.177065587457337</v>
+        <v>3.118187918204153</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.460276001072111</v>
+        <v>1.500486736302761</v>
       </c>
       <c r="G2092" t="n">
-        <v>4.838167607472278</v>
+        <v>4.840353706946759</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240919.xlsx
+++ b/tame_output/ON/bt/strategyON_20240919.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.6%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.8%</t>
+          <t>-581.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>-59.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.1%</t>
+          <t>-320.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-69.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>131.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>119.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>131.7%</t>
         </is>
       </c>
     </row>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.28421076575722</v>
+        <v>-5.235223797101618</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.537358983434678</v>
+        <v>1.556953770896919</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2711232383499265</v>
+        <v>0.320110207005529</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.814073657061271</v>
+        <v>3.843465838254632</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.174204482279999</v>
+        <v>-5.125217513624396</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.573514384069743</v>
+        <v>1.593109171531983</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2943278102672017</v>
+        <v>0.3433147789228042</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.820149287455811</v>
+        <v>3.849541468649173</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.031144906539073</v>
+        <v>-4.982157937883471</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.634988225088087</v>
+        <v>1.654583012550328</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.302341236857181</v>
+        <v>0.3513282055127835</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.829207354131773</v>
+        <v>3.858599535325135</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.729698181067235</v>
+        <v>-4.680711212411634</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.762827798159358</v>
+        <v>1.782422585621599</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6037879623290182</v>
+        <v>0.6527749309846207</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.017336272297412</v>
+        <v>4.046728453490773</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.754288425302419</v>
+        <v>-4.705301456646818</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.753962878217995</v>
+        <v>1.773557665680236</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6037879623290182</v>
+        <v>0.6527749309846207</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.018307450050122</v>
+        <v>4.047699631243484</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.703250049295899</v>
+        <v>-4.654263080640297</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.775221133000359</v>
+        <v>1.7948159204626</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6037879623290182</v>
+        <v>0.6527749309846207</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.019150354429877</v>
+        <v>4.048542535623239</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.662110754429268</v>
+        <v>-4.613123785773666</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.810714949821157</v>
+        <v>1.830309737283397</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.644927257195649</v>
+        <v>0.6939142258512515</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.062872030224002</v>
+        <v>4.092264211417363</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.565475842410628</v>
+        <v>-4.516488873755026</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.665552910752547</v>
+        <v>1.685147698214788</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.741562169214289</v>
+        <v>0.7905491378698914</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.93703697355912</v>
+        <v>3.966429154752482</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.49643783146216</v>
+        <v>-4.447450862806559</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.696670159205899</v>
+        <v>1.716264946668139</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.810600180162757</v>
+        <v>0.8595871488183595</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.981961824202165</v>
+        <v>4.011354005395527</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833454</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.331941497271198</v>
+        <v>-4.282954528615597</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.746895511958366</v>
+        <v>1.766490299420606</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9750965143537189</v>
+        <v>1.024083483009322</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.065086443792825</v>
+        <v>4.094478624986186</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.254842895729325</v>
+        <v>-4.205855927073724</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.776922663011545</v>
+        <v>1.796517450473785</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9750965143537189</v>
+        <v>1.024083483009322</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.064274154229254</v>
+        <v>4.093666335422616</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.265228090619215</v>
+        <v>-4.216241121963614</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.782637364180661</v>
+        <v>1.802232151642902</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9647113194638296</v>
+        <v>1.013698288119432</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.067911816420393</v>
+        <v>4.097303997613754</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.28381624934144</v>
+        <v>-4.234829280685839</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.846039106468196</v>
+        <v>1.865633893930437</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9461231607416043</v>
+        <v>0.9951101293972067</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.127595926963483</v>
+        <v>4.156988108156844</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.284114796037476</v>
+        <v>-4.235127827381874</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.842788698608081</v>
+        <v>1.862383486070321</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9458246140455684</v>
+        <v>0.9948115827011708</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.12428580976416</v>
+        <v>4.153677990957521</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.183291662347048</v>
+        <v>-4.134304693691447</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.887648847023643</v>
+        <v>1.907243634485884</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9582888295299222</v>
+        <v>1.007275798185525</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.136295233994164</v>
+        <v>4.165687415187525</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.992510301594641</v>
+        <v>-3.943523332939039</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.964090644803149</v>
+        <v>1.98368543226539</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.149070190282329</v>
+        <v>1.198057158937932</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.250893303924151</v>
+        <v>4.280285485117513</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.885546943745219</v>
+        <v>-3.836559975089617</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.986712833680515</v>
+        <v>2.006307621142756</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.207534798242131</v>
+        <v>1.256521766897734</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.265808914437629</v>
+        <v>4.295201095630991</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.830216355843457</v>
+        <v>-3.781229387187855</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.043812005453278</v>
+        <v>2.063406792915519</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.262865386143893</v>
+        <v>1.311852354799496</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.333974203790745</v>
+        <v>4.363366384984106</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.818162228930494</v>
+        <v>-3.769175260274892</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.042320224119901</v>
+        <v>2.061915011582141</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.274919513056856</v>
+        <v>1.323906481712458</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.33489324783996</v>
+        <v>4.364285429033322</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.859317348498715</v>
+        <v>-3.810330379843113</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.027738806476748</v>
+        <v>2.047333593938989</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.233764393488635</v>
+        <v>1.282751362144237</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.312080806283164</v>
+        <v>4.341472987476525</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.791268785807185</v>
+        <v>-3.742281817151583</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.067809257431243</v>
+        <v>2.087404044893483</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.301812956180165</v>
+        <v>1.350799924835767</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.365760969775963</v>
+        <v>4.395153150969326</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.022869178976686</v>
+        <v>-3.973882210321085</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.995371770337036</v>
+        <v>2.014966557799277</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.301812956180165</v>
+        <v>1.350799924835767</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.385963639949558</v>
+        <v>4.41535582114292</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.072920724505906</v>
+        <v>-4.023933755850305</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.958957388192231</v>
+        <v>1.978552175654471</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.301812956180165</v>
+        <v>1.350799924835767</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.36956987601644</v>
+        <v>4.398962057209801</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.24802755708235</v>
+        <v>-4.199040588426749</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.849166568755119</v>
+        <v>1.86876135621736</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.301812956180165</v>
+        <v>1.350799924835767</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.329821789609906</v>
+        <v>4.359213970803268</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.051927403651828</v>
+        <v>-4.002940434996226</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.934629249124268</v>
+        <v>1.954224036586509</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.497913109610688</v>
+        <v>1.54690007826629</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.45450450066516</v>
+        <v>4.483896681858522</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.898902011538544</v>
+        <v>-3.849915042882942</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.095010405542487</v>
+        <v>2.114605193004727</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.650938501723972</v>
+        <v>1.699925470379574</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.645490735506035</v>
+        <v>4.674882916699397</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.927209325411813</v>
+        <v>-3.878222356756212</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.271153704901471</v>
+        <v>2.290748492363711</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.650938501723972</v>
+        <v>1.699925470379574</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.832956960414328</v>
+        <v>4.862349141607689</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.093802550525336</v>
+        <v>-4.044815581869734</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.173919366210145</v>
+        <v>2.193514153672385</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.484345276610449</v>
+        <v>1.533332245266052</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.702403976700297</v>
+        <v>4.731796157893658</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.07076675716377</v>
+        <v>-4.021779788508169</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.186810086216489</v>
+        <v>2.206404873678729</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.484345276610449</v>
+        <v>1.533332245266052</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.706080379362015</v>
+        <v>4.735472560555376</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.041520776708073</v>
+        <v>-3.992533808052472</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.196126533522263</v>
+        <v>2.215721320984503</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.484345276610449</v>
+        <v>1.533332245266052</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.70369843448551</v>
+        <v>4.733090615678871</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.148446324585924</v>
+        <v>-4.099459355930324</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.150649553528758</v>
+        <v>2.170244340990998</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.377419728732598</v>
+        <v>1.426406697388201</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.636836344916434</v>
+        <v>4.666228526109796</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.293464883093173</v>
+        <v>-4.244477914437573</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.094070932269092</v>
+        <v>2.113665719731332</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.232401170225349</v>
+        <v>1.281388138880952</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.55125401195532</v>
+        <v>4.580646193148681</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.41180664887789</v>
+        <v>-4.36281968022229</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.146665465212958</v>
+        <v>2.166260252675198</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.24308720878824</v>
+        <v>1.292074177443842</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.657596874350807</v>
+        <v>4.686989055544168</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.463217071198598</v>
+        <v>-4.414230102542998</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.123886993410614</v>
+        <v>2.143481780872854</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.24308720878824</v>
+        <v>1.292074177443842</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.655382571476745</v>
+        <v>4.684774752670107</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.54263652240635</v>
+        <v>-4.49364955375075</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.092022341001803</v>
+        <v>2.111617128464043</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.24308720878824</v>
+        <v>1.292074177443842</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.655285699551035</v>
+        <v>4.684677880744396</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.638099520323568</v>
+        <v>-4.589112551667967</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.053831035392959</v>
+        <v>2.073425822855198</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.24308720878824</v>
+        <v>1.292074177443842</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.655279593109078</v>
+        <v>4.684671774302439</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.573723609472853</v>
+        <v>-4.524736640817252</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.077677796295855</v>
+        <v>2.097272583758095</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.307463119638955</v>
+        <v>1.356450088294557</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.692001536182118</v>
+        <v>4.721393717375479</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.629092771605047</v>
+        <v>-4.580105802949446</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.061263949190704</v>
+        <v>2.080858736652945</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.307463119638955</v>
+        <v>1.356450088294557</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.697735353929844</v>
+        <v>4.727127535123206</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.674530551435874</v>
+        <v>-4.625543582780273</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.042627200601306</v>
+        <v>2.062221988063546</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.264618128960795</v>
+        <v>1.313605097616398</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.67156672286588</v>
+        <v>4.700958904059243</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.586323717288296</v>
+        <v>-4.537336748632695</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.097784327110656</v>
+        <v>2.117379114572896</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.264618128960795</v>
+        <v>1.313605097616398</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.691441115716199</v>
+        <v>4.720833296909561</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.480288722082986</v>
+        <v>-4.431301753427386</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.123899025717507</v>
+        <v>2.143493813179748</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.264618128960795</v>
+        <v>1.313605097616398</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.675141816240927</v>
+        <v>4.704533997434289</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.297077058949891</v>
+        <v>-4.248090090294291</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.199614640434791</v>
+        <v>2.219209427897031</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.264618128960795</v>
+        <v>1.313605097616398</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.677572765704973</v>
+        <v>4.706964946898334</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.22535561193604</v>
+        <v>-4.17636864328044</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.194094405088221</v>
+        <v>2.213689192550461</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.336339575974646</v>
+        <v>1.385326544630249</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.686396819761173</v>
+        <v>4.715789000954534</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.202982586328334</v>
+        <v>-4.153995617672734</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.149959361252475</v>
+        <v>2.169554148714715</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.347595327087547</v>
+        <v>1.39658229574315</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.640066016350086</v>
+        <v>4.669458197543447</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.235998882239079</v>
+        <v>-4.187011913583478</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.321951047773533</v>
+        <v>2.341545835235773</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.278157950420796</v>
+        <v>1.327144919076398</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.78360179523539</v>
+        <v>4.812993976428752</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.22447124658947</v>
+        <v>-4.17548427793387</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.318483327861625</v>
+        <v>2.338078115323865</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.337158608622158</v>
+        <v>1.386145577277761</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.810923415984456</v>
+        <v>4.840315597177818</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236292</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.321812747931839</v>
+        <v>-4.272825779276238</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.283214839846466</v>
+        <v>2.302809627308706</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.29273842645667</v>
+        <v>1.341725395112273</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.787939419206952</v>
+        <v>4.817331600400314</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942768</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.407668777271805</v>
+        <v>-4.358681808616205</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.250123510303318</v>
+        <v>2.269718297765558</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.250362357230535</v>
+        <v>1.299349325886137</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.763764859864109</v>
+        <v>4.79315704105747</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.416505574687925</v>
+        <v>-4.367518606032324</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.229007993157372</v>
+        <v>2.248602780619612</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.242920184589184</v>
+        <v>1.291907153244787</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.7417187580998</v>
+        <v>4.771110939293162</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.507888137253383</v>
+        <v>-4.458901168597783</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.202619479176238</v>
+        <v>2.222214266638478</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.206355299869839</v>
+        <v>1.255342268525442</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.729944338313243</v>
+        <v>4.759336519506604</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
         <v>4.033297452870161</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.496181419266377</v>
+        <v>-4.447194450610777</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.234468460849862</v>
+        <v>2.254063248312102</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.218062017856846</v>
+        <v>1.267048986512449</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.764134663584269</v>
+        <v>4.793526844777631</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.036329791601566</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.396517915182715</v>
+        <v>-4.347530946527114</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.277366201214732</v>
+        <v>2.296960988676972</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.281249101060532</v>
+        <v>1.330236069716135</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.805079252237886</v>
+        <v>4.834471433431247</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.249234624879625</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.406834013349067</v>
+        <v>-4.357847044693466</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.48614459522625</v>
+        <v>2.50573938268849</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.281249101060532</v>
+        <v>1.330236069716135</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.017984085515945</v>
+        <v>5.047376266709306</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.248413291791715</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.406740045331694</v>
+        <v>-4.357753076676094</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.485360849345289</v>
+        <v>2.504955636807529</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.28161896240785</v>
+        <v>1.330605931063453</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.017384669236425</v>
+        <v>5.046776850429787</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.242645277736068</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.413958869531538</v>
+        <v>-4.364971900875938</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.476705305609705</v>
+        <v>2.496300093071945</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.28161896240785</v>
+        <v>1.330605931063453</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.011616655180779</v>
+        <v>5.04100883637414</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.242645277736068</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.4130104464135</v>
+        <v>-4.364023477757899</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.47708467485692</v>
+        <v>2.496679462319161</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.28161896240785</v>
+        <v>1.330605931063453</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.011616655180779</v>
+        <v>5.04100883637414</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.25537288571716</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.570078904669124</v>
+        <v>-4.521091936013523</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.426984899535763</v>
+        <v>2.446579686998003</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.28161896240785</v>
+        <v>1.330605931063453</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.024344263161871</v>
+        <v>5.053736444355232</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.257318884141548</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.564086657880313</v>
+        <v>-4.515099689224711</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.431327796675675</v>
+        <v>2.450922584137916</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.28161896240785</v>
+        <v>1.330605931063453</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.026290261586259</v>
+        <v>5.05568244277962</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.250973020159317</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.475528696749545</v>
+        <v>-4.426541728093944</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.460405117145751</v>
+        <v>2.479999904607991</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.28161896240785</v>
+        <v>1.330605931063453</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.019944397604028</v>
+        <v>5.049336578797389</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.250281697598313</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.457769619246471</v>
+        <v>-4.40878265059087</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.466817425585976</v>
+        <v>2.486412213048217</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.28161896240785</v>
+        <v>1.330605931063453</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.019253075043023</v>
+        <v>5.048645256236385</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.263063883506899</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.358139468197403</v>
+        <v>-4.309152499541802</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.51945167191419</v>
+        <v>2.539046459376431</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.381249113456918</v>
+        <v>1.430236082112521</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.091813351581051</v>
+        <v>5.121205532774412</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.452218149005626</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.407538976886414</v>
+        <v>-4.358552008230813</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.688846133937312</v>
+        <v>2.708440921399553</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.391507946888663</v>
+        <v>1.440494915544265</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.287122917138824</v>
+        <v>5.316515098332186</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.439406822108488</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.200854503244038</v>
+        <v>-4.151867534588437</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.758708596497125</v>
+        <v>2.778303383959365</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.598192420531038</v>
+        <v>1.647179389186641</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.398322274427112</v>
+        <v>5.427714455620473</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.441408335762593</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.235011398241564</v>
+        <v>-4.186024429585963</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.747047352152219</v>
+        <v>2.76664213961446</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.514608650990226</v>
+        <v>1.563595619645829</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.350173526356729</v>
+        <v>5.37956570755009</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.79490544975226</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.142421919180108</v>
+        <v>-4.093434950524506</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.137580257766469</v>
+        <v>3.15717504522871</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.514608650990226</v>
+        <v>1.563595619645829</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.703670640346396</v>
+        <v>5.733062821539757</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.799468561319364</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.202310547003658</v>
+        <v>-4.153323578348057</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.118187918204153</v>
+        <v>3.137782705666393</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.500486736302761</v>
+        <v>1.549473704958364</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.699760603101021</v>
+        <v>5.729152784294382</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.787804892116936</v>
+        <v>3.902080662191882</v>
       </c>
       <c r="C2092" t="n">
         <v>4.847289909960391</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.202310547003658</v>
+        <v>-4.203147563793774</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.118187918204153</v>
+        <v>3.165674460129134</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.500486736302761</v>
+        <v>1.549473704958364</v>
       </c>
       <c r="G2092" t="n">
-        <v>4.840353706946759</v>
+        <v>5.77697413293541</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240919.xlsx
+++ b/tame_output/ON/bt/strategyON_20240919.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>112.1%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>173.1%</t>
+          <t>174.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>122.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.9%</t>
+          <t>-576.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-59.7%</t>
+          <t>-55.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>114.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.6%</t>
+          <t>-320.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-69.0%</t>
+          <t>-74.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.7%</t>
+          <t>131.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>119.7%</t>
+          <t>119.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>131.7%</t>
+          <t>130.2%</t>
         </is>
       </c>
     </row>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.235223797101618</v>
+        <v>-5.227463430708024</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.556953770896919</v>
+        <v>1.560057917454357</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.320110207005529</v>
+        <v>0.3278705733991228</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.843465838254632</v>
+        <v>3.848122058090789</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.125217513624396</v>
+        <v>-5.117457147230803</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.593109171531983</v>
+        <v>1.596213318089421</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3433147789228042</v>
+        <v>0.351075145316398</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.849541468649173</v>
+        <v>3.854197688485329</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.982157937883471</v>
+        <v>-4.974397571489877</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.654583012550328</v>
+        <v>1.657687159107765</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3513282055127835</v>
+        <v>0.3590885719063773</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.858599535325135</v>
+        <v>3.863255755161291</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.680711212411634</v>
+        <v>-4.67295084601804</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.782422585621599</v>
+        <v>1.785526732179036</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6527749309846207</v>
+        <v>0.6605352973782146</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.046728453490773</v>
+        <v>4.051384673326929</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.705301456646818</v>
+        <v>-4.697541090253224</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.773557665680236</v>
+        <v>1.776661812237673</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6527749309846207</v>
+        <v>0.6605352973782146</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.047699631243484</v>
+        <v>4.05235585107964</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.654263080640297</v>
+        <v>-4.646502714246703</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.7948159204626</v>
+        <v>1.797920067020037</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6527749309846207</v>
+        <v>0.6605352973782146</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.048542535623239</v>
+        <v>4.053198755459396</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.613123785773666</v>
+        <v>-4.605363419380073</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.830309737283397</v>
+        <v>1.833413883840835</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6939142258512515</v>
+        <v>0.7016745922448454</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.092264211417363</v>
+        <v>4.096920431253519</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.516488873755026</v>
+        <v>-4.508728507361432</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.685147698214788</v>
+        <v>1.688251844772225</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7905491378698914</v>
+        <v>0.7983095042634853</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.966429154752482</v>
+        <v>3.971085374588638</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.447450862806559</v>
+        <v>-4.439690496412965</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.716264946668139</v>
+        <v>1.719369093225577</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8595871488183595</v>
+        <v>0.8673475152119534</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.011354005395527</v>
+        <v>4.016010225231683</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.282954528615597</v>
+        <v>-4.275194162222003</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.766490299420606</v>
+        <v>1.769594445978044</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.024083483009322</v>
+        <v>1.031843849402915</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.094478624986186</v>
+        <v>4.099134844822343</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.205855927073724</v>
+        <v>-4.19809556068013</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.796517450473785</v>
+        <v>1.799621597031223</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.024083483009322</v>
+        <v>1.031843849402915</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.093666335422616</v>
+        <v>4.098322555258772</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.216241121963614</v>
+        <v>-4.20848075557002</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.802232151642902</v>
+        <v>1.805336298200339</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.013698288119432</v>
+        <v>1.021458654513026</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.097303997613754</v>
+        <v>4.101960217449911</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.234829280685839</v>
+        <v>-4.227068914292245</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.865633893930437</v>
+        <v>1.868738040487875</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9951101293972067</v>
+        <v>1.002870495790801</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.156988108156844</v>
+        <v>4.161644327993001</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.235127827381874</v>
+        <v>-4.227367460988281</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.862383486070321</v>
+        <v>1.865487632627759</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9948115827011708</v>
+        <v>1.002571949094765</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.153677990957521</v>
+        <v>4.158334210793678</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.134304693691447</v>
+        <v>-4.126544327297853</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.907243634485884</v>
+        <v>1.910347781043321</v>
       </c>
       <c r="F2040" t="n">
-        <v>1.007275798185525</v>
+        <v>1.015036164579119</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.165687415187525</v>
+        <v>4.170343635023682</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.943523332939039</v>
+        <v>-3.935762966545445</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.98368543226539</v>
+        <v>1.986789578822827</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.198057158937932</v>
+        <v>1.205817525331526</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.280285485117513</v>
+        <v>4.28494170495367</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.836559975089617</v>
+        <v>-3.828799608696023</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.006307621142756</v>
+        <v>2.009411767700193</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.256521766897734</v>
+        <v>1.264282133291327</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.295201095630991</v>
+        <v>4.299857315467147</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.781229387187855</v>
+        <v>-3.773469020794261</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.063406792915519</v>
+        <v>2.066510939472956</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.311852354799496</v>
+        <v>1.319612721193089</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.363366384984106</v>
+        <v>4.368022604820262</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.769175260274892</v>
+        <v>-3.761414893881299</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.061915011582141</v>
+        <v>2.065019158139579</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.323906481712458</v>
+        <v>1.331666848106052</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.364285429033322</v>
+        <v>4.368941648869478</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.810330379843113</v>
+        <v>-3.80257001344952</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.047333593938989</v>
+        <v>2.050437740496426</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.282751362144237</v>
+        <v>1.290511728537831</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.341472987476525</v>
+        <v>4.346129207312681</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.742281817151583</v>
+        <v>-3.73452145075799</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.087404044893483</v>
+        <v>2.090508191450921</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.350799924835767</v>
+        <v>1.358560291229361</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.395153150969326</v>
+        <v>4.399809370805482</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-3.973882210321085</v>
+        <v>-3.966121843927491</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.014966557799277</v>
+        <v>2.018070704356715</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.350799924835767</v>
+        <v>1.358560291229361</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.41535582114292</v>
+        <v>4.420012040979076</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.023933755850305</v>
+        <v>-4.016173389456711</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.978552175654471</v>
+        <v>1.981656322211909</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.350799924835767</v>
+        <v>1.358560291229361</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.398962057209801</v>
+        <v>4.403618277045958</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.199040588426749</v>
+        <v>-4.191280222033155</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.86876135621736</v>
+        <v>1.871865502774797</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.350799924835767</v>
+        <v>1.358560291229361</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.359213970803268</v>
+        <v>4.363870190639425</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.002940434996226</v>
+        <v>-3.995180068602632</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.954224036586509</v>
+        <v>1.957328183143947</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.54690007826629</v>
+        <v>1.554660444659884</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.483896681858522</v>
+        <v>4.488552901694678</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.849915042882942</v>
+        <v>-3.842154676489348</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.114605193004727</v>
+        <v>2.117709339562165</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.699925470379574</v>
+        <v>1.707685836773168</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.674882916699397</v>
+        <v>4.679539136535553</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.878222356756212</v>
+        <v>-3.870461990362618</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.290748492363711</v>
+        <v>2.293852638921149</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.699925470379574</v>
+        <v>1.707685836773168</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.862349141607689</v>
+        <v>4.867005361443845</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.044815581869734</v>
+        <v>-4.037055215476141</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.193514153672385</v>
+        <v>2.196618300229823</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.533332245266052</v>
+        <v>1.541092611659646</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.731796157893658</v>
+        <v>4.736452377729815</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.021779788508169</v>
+        <v>-4.014019422114575</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.206404873678729</v>
+        <v>2.209509020236167</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.533332245266052</v>
+        <v>1.541092611659646</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.735472560555376</v>
+        <v>4.740128780391533</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-3.992533808052472</v>
+        <v>-3.984773441658878</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.215721320984503</v>
+        <v>2.218825467541941</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.533332245266052</v>
+        <v>1.541092611659646</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.733090615678871</v>
+        <v>4.737746835515027</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.099459355930324</v>
+        <v>-4.09169898953673</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.170244340990998</v>
+        <v>2.173348487548435</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.426406697388201</v>
+        <v>1.434167063781794</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.666228526109796</v>
+        <v>4.670884745945952</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.244477914437573</v>
+        <v>-4.236717548043979</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.113665719731332</v>
+        <v>2.11676986628877</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.281388138880952</v>
+        <v>1.289148505274546</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.580646193148681</v>
+        <v>4.585302412984837</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.36281968022229</v>
+        <v>-4.355059313828696</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.166260252675198</v>
+        <v>2.169364399232636</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.292074177443842</v>
+        <v>1.299834543837436</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.686989055544168</v>
+        <v>4.691645275380324</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.414230102542998</v>
+        <v>-4.406469736149404</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.143481780872854</v>
+        <v>2.146585927430292</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.292074177443842</v>
+        <v>1.299834543837436</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.684774752670107</v>
+        <v>4.689430972506264</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.49364955375075</v>
+        <v>-4.485889187357156</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.111617128464043</v>
+        <v>2.114721275021481</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.292074177443842</v>
+        <v>1.299834543837436</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.684677880744396</v>
+        <v>4.689334100580552</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298395</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.589112551667967</v>
+        <v>-4.524197895330436</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.073425822855198</v>
+        <v>2.099391685390211</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.292074177443842</v>
+        <v>1.299834543837436</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.684671774302439</v>
+        <v>4.689327994138596</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.524736640817252</v>
+        <v>-4.459821984479721</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.097272583758095</v>
+        <v>2.123238446293108</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.356450088294557</v>
+        <v>1.364210454688151</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.721393717375479</v>
+        <v>4.726049937211635</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.580105802949446</v>
+        <v>-4.515191146611914</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.080858736652945</v>
+        <v>2.106824599187958</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.356450088294557</v>
+        <v>1.364210454688151</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.727127535123206</v>
+        <v>4.731783754959362</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.625543582780273</v>
+        <v>-4.560628926442742</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.062221988063546</v>
+        <v>2.088187850598559</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.313605097616398</v>
+        <v>1.321365464009992</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.700958904059243</v>
+        <v>4.705615123895399</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.537336748632695</v>
+        <v>-4.472422092295163</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.117379114572896</v>
+        <v>2.143344977107909</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.313605097616398</v>
+        <v>1.321365464009992</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.720833296909561</v>
+        <v>4.725489516745717</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.431301753427386</v>
+        <v>-4.366387097089854</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.143493813179748</v>
+        <v>2.16945967571476</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.313605097616398</v>
+        <v>1.321365464009992</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.704533997434289</v>
+        <v>4.709190217270445</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.248090090294291</v>
+        <v>-4.183175433956759</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.219209427897031</v>
+        <v>2.245175290432044</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.313605097616398</v>
+        <v>1.321365464009992</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.706964946898334</v>
+        <v>4.71162116673449</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.17636864328044</v>
+        <v>-4.111453986942908</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.213689192550461</v>
+        <v>2.239655055085474</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.385326544630249</v>
+        <v>1.393086911023842</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.715789000954534</v>
+        <v>4.720445220790691</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.153995617672734</v>
+        <v>-4.089080961335202</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.169554148714715</v>
+        <v>2.195520011249728</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.39658229574315</v>
+        <v>1.404342662136744</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.669458197543447</v>
+        <v>4.674114417379603</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.187011913583478</v>
+        <v>-4.122097257245946</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.341545835235773</v>
+        <v>2.367511697770786</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.327144919076398</v>
+        <v>1.334905285469992</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.812993976428752</v>
+        <v>4.817650196264908</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883673</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.17548427793387</v>
+        <v>-4.110569621596338</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.338078115323865</v>
+        <v>2.364043977858878</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.386145577277761</v>
+        <v>1.393905943671355</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.840315597177818</v>
+        <v>4.844971817013974</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236292</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.272825779276238</v>
+        <v>-4.207911122938707</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.302809627308706</v>
+        <v>2.328775489843719</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.341725395112273</v>
+        <v>1.349485761505866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.817331600400314</v>
+        <v>4.82198782023647</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.358681808616205</v>
+        <v>-4.293767152278673</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.269718297765558</v>
+        <v>2.295684160300571</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.299349325886137</v>
+        <v>1.307109692279731</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.79315704105747</v>
+        <v>4.797813260893627</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.367518606032324</v>
+        <v>-4.302603949694793</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.248602780619612</v>
+        <v>2.274568643154625</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.291907153244787</v>
+        <v>1.299667519638381</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.771110939293162</v>
+        <v>4.775767159129318</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.458901168597783</v>
+        <v>-4.393986512260251</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.222214266638478</v>
+        <v>2.248180129173491</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.255342268525442</v>
+        <v>1.263102634919036</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.759336519506604</v>
+        <v>4.763992739342761</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889187</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.033297452870161</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.447194450610777</v>
+        <v>-4.435571886732641</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.254063248312102</v>
+        <v>2.333674237208802</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.267048986512449</v>
+        <v>1.221517260446646</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.793526844777631</v>
+        <v>4.841169772483594</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.036329791601566</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.347530946527114</v>
+        <v>-4.335908382648978</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.296960988676972</v>
+        <v>2.376571977573672</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.330236069716135</v>
+        <v>1.284704343650333</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.834471433431247</v>
+        <v>4.882114361137211</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.249234624879625</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.357847044693466</v>
+        <v>-4.34622448081533</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.50573938268849</v>
+        <v>2.585350371585189</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.330236069716135</v>
+        <v>1.284704343650333</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.047376266709306</v>
+        <v>5.095019194415269</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.248413291791715</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.357753076676094</v>
+        <v>-4.346130512797957</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.504955636807529</v>
+        <v>2.584566625704228</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.330605931063453</v>
+        <v>1.285074204997651</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.046776850429787</v>
+        <v>5.09441977813575</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.242645277736068</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.364971900875938</v>
+        <v>-4.353349336997802</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.496300093071945</v>
+        <v>2.575911081968644</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.330605931063453</v>
+        <v>1.285074204997651</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.04100883637414</v>
+        <v>5.088651764080104</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.242645277736068</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.364023477757899</v>
+        <v>-4.352400913879763</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.496679462319161</v>
+        <v>2.57629045121586</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.330605931063453</v>
+        <v>1.285074204997651</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.04100883637414</v>
+        <v>5.088651764080104</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.25537288571716</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.521091936013523</v>
+        <v>-4.509469372135387</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.446579686998003</v>
+        <v>2.526190675894702</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.330605931063453</v>
+        <v>1.285074204997651</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.053736444355232</v>
+        <v>5.101379372061196</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.257318884141548</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.515099689224711</v>
+        <v>-4.503477125346575</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.450922584137916</v>
+        <v>2.530533573034615</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.330605931063453</v>
+        <v>1.285074204997651</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.05568244277962</v>
+        <v>5.103325370485583</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.250973020159317</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.426541728093944</v>
+        <v>-4.414919164215807</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.479999904607991</v>
+        <v>2.55961089350469</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.330605931063453</v>
+        <v>1.285074204997651</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.049336578797389</v>
+        <v>5.096979506503352</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.250281697598313</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.40878265059087</v>
+        <v>-4.397160086712733</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.486412213048217</v>
+        <v>2.566023201944915</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.330605931063453</v>
+        <v>1.285074204997651</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.048645256236385</v>
+        <v>5.096288183942348</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.263063883506899</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.309152499541802</v>
+        <v>-4.297529935663666</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.539046459376431</v>
+        <v>2.61865744827313</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.430236082112521</v>
+        <v>1.384704356046718</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.121205532774412</v>
+        <v>5.168848460480375</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.452218149005626</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.358552008230813</v>
+        <v>-4.346929444352677</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.708440921399553</v>
+        <v>2.788051910296252</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.440494915544265</v>
+        <v>1.394963189478463</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.316515098332186</v>
+        <v>5.364158026038148</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.439406822108488</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.151867534588437</v>
+        <v>-4.140244970710301</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.778303383959365</v>
+        <v>2.857914372856064</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.647179389186641</v>
+        <v>1.601647663120839</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.427714455620473</v>
+        <v>5.475357383326436</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.441408335762593</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.186024429585963</v>
+        <v>-4.174401865707827</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.76664213961446</v>
+        <v>2.846253128511159</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.563595619645829</v>
+        <v>1.518063893580027</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.37956570755009</v>
+        <v>5.427208635256053</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.79490544975226</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.093434950524506</v>
+        <v>-4.08181238664637</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.15717504522871</v>
+        <v>3.236786034125409</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.563595619645829</v>
+        <v>1.518063893580027</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.733062821539757</v>
+        <v>5.780705749245721</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108666</v>
+        <v>3.809055905108668</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.799468561319364</v>
+        <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.153323578348057</v>
+        <v>-4.141701014469921</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.137782705666393</v>
+        <v>3.217393694563092</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.549473704958364</v>
+        <v>1.503941978892562</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.729152784294382</v>
+        <v>5.776795712000345</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.902080662191882</v>
+        <v>3.907929210390006</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.847289909960391</v>
+        <v>4.863402328458761</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.203147563793774</v>
+        <v>-4.148121556399258</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.165674460129134</v>
+        <v>3.20379728158531</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.549473704958364</v>
+        <v>1.497521436963224</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.77697413293541</v>
+        <v>5.761915190636696</v>
       </c>
     </row>
   </sheetData>
